--- a/PUEYRREDON 1494/Mayo/PUEYRREDON MAYO.xlsx
+++ b/PUEYRREDON 1494/Mayo/PUEYRREDON MAYO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\PUEYRREDON 1494\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C5C70E-BCD9-45C3-ACD4-551F4F943C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7637B611-4A74-4DA7-BA27-459CB954B51B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="157">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -493,6 +493,9 @@
   </si>
   <si>
     <t>Tanques</t>
+  </si>
+  <si>
+    <t>Camara de seguridad Imou Ipc-f22p-d</t>
   </si>
 </sst>
 </file>
@@ -1140,7 +1143,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="190">
+  <cellXfs count="191">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1345,6 +1348,8 @@
     <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1396,6 +1401,27 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1405,12 +1431,6 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1432,23 +1452,7 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -1898,49 +1902,49 @@
       <c r="E7" s="21"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="155" t="s">
+      <c r="B9" s="157" t="s">
         <v>150</v>
       </c>
-      <c r="C9" s="155"/>
+      <c r="C9" s="157"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="155"/>
-      <c r="C10" s="155"/>
+      <c r="B10" s="157"/>
+      <c r="C10" s="157"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="155"/>
-      <c r="C11" s="155"/>
+      <c r="B11" s="157"/>
+      <c r="C11" s="157"/>
     </row>
     <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="154" t="s">
+      <c r="A14" s="156" t="s">
         <v>124</v>
       </c>
-      <c r="B14" s="154"/>
-      <c r="C14" s="154"/>
-      <c r="D14" s="154"/>
-      <c r="E14" s="154"/>
+      <c r="B14" s="156"/>
+      <c r="C14" s="156"/>
+      <c r="D14" s="156"/>
+      <c r="E14" s="156"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="154"/>
-      <c r="B15" s="154"/>
-      <c r="C15" s="154"/>
-      <c r="D15" s="154"/>
-      <c r="E15" s="154"/>
+      <c r="A15" s="156"/>
+      <c r="B15" s="156"/>
+      <c r="C15" s="156"/>
+      <c r="D15" s="156"/>
+      <c r="E15" s="156"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="154"/>
-      <c r="B16" s="154"/>
-      <c r="C16" s="154"/>
-      <c r="D16" s="154"/>
-      <c r="E16" s="154"/>
+      <c r="A16" s="156"/>
+      <c r="B16" s="156"/>
+      <c r="C16" s="156"/>
+      <c r="D16" s="156"/>
+      <c r="E16" s="156"/>
     </row>
     <row r="17" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="154"/>
-      <c r="B17" s="154"/>
-      <c r="C17" s="154"/>
-      <c r="D17" s="154"/>
-      <c r="E17" s="154"/>
+      <c r="A17" s="156"/>
+      <c r="B17" s="156"/>
+      <c r="C17" s="156"/>
+      <c r="D17" s="156"/>
+      <c r="E17" s="156"/>
     </row>
     <row r="18" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
@@ -2090,10 +2094,10 @@
       <c r="E33" s="76"/>
     </row>
     <row r="34" spans="1:7" s="44" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="156" t="s">
+      <c r="A34" s="158" t="s">
         <v>146</v>
       </c>
-      <c r="B34" s="157"/>
+      <c r="B34" s="159"/>
       <c r="C34" s="63"/>
       <c r="D34" s="149">
         <v>87562.7</v>
@@ -2101,10 +2105,10 @@
       <c r="E34" s="126"/>
     </row>
     <row r="35" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="156" t="s">
+      <c r="A35" s="158" t="s">
         <v>140</v>
       </c>
-      <c r="B35" s="157"/>
+      <c r="B35" s="159"/>
       <c r="C35" s="63"/>
       <c r="D35" s="150">
         <v>6646.91</v>
@@ -2138,7 +2142,7 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="61"/>
-      <c r="D38" s="188">
+      <c r="D38" s="154">
         <v>371131.27</v>
       </c>
       <c r="E38" s="129" t="s">
@@ -2154,7 +2158,7 @@
         <v>116</v>
       </c>
       <c r="C39" s="5"/>
-      <c r="D39" s="188">
+      <c r="D39" s="154">
         <v>19236.05</v>
       </c>
       <c r="E39" s="130" t="s">
@@ -2170,7 +2174,7 @@
         <v>117</v>
       </c>
       <c r="C40" s="5"/>
-      <c r="D40" s="188">
+      <c r="D40" s="154">
         <v>62013.71</v>
       </c>
       <c r="E40" s="130" t="str">
@@ -2187,7 +2191,7 @@
         <v>118</v>
       </c>
       <c r="C41" s="5"/>
-      <c r="D41" s="188">
+      <c r="D41" s="154">
         <v>3847.21</v>
       </c>
       <c r="E41" s="131" t="str">
@@ -2217,23 +2221,23 @@
       <c r="E43" s="105"/>
     </row>
     <row r="44" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="189" t="s">
+      <c r="A44" s="155" t="s">
         <v>154</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
-      <c r="D44" s="188">
+      <c r="D44" s="154">
         <v>33360</v>
       </c>
       <c r="E44" s="109"/>
     </row>
     <row r="45" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="189" t="s">
+      <c r="A45" s="155" t="s">
         <v>154</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
-      <c r="D45" s="188">
+      <c r="D45" s="154">
         <v>36700</v>
       </c>
       <c r="E45" s="109"/>
@@ -2265,19 +2269,19 @@
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="189" t="s">
+      <c r="A48" s="155" t="s">
         <v>155</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
-      <c r="D48" s="188">
+      <c r="D48" s="154">
         <v>1000000</v>
       </c>
       <c r="E48" s="109"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" s="160"/>
-      <c r="B49" s="161"/>
+      <c r="A49" s="162"/>
+      <c r="B49" s="163"/>
       <c r="C49" s="64"/>
       <c r="D49" s="108"/>
       <c r="E49" s="106"/>
@@ -2326,10 +2330,14 @@
       <c r="E53" s="127"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54" s="61"/>
+      <c r="A54" s="61" t="s">
+        <v>156</v>
+      </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
-      <c r="D54" s="42"/>
+      <c r="D54" s="190">
+        <v>47334</v>
+      </c>
       <c r="E54" s="106"/>
     </row>
     <row r="55" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2341,7 +2349,7 @@
       <c r="D55" s="38"/>
       <c r="E55" s="111">
         <f>SUM(D52:D54)</f>
-        <v>2940</v>
+        <v>50274</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2420,7 +2428,7 @@
       <c r="D63" s="119"/>
       <c r="E63" s="120">
         <f>(SUM(E28:E61))</f>
-        <v>3230136</v>
+        <v>3277470</v>
       </c>
       <c r="F63" s="51"/>
       <c r="G63" s="134"/>
@@ -2444,22 +2452,22 @@
       <c r="E66" s="122"/>
     </row>
     <row r="67" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="163" t="s">
+      <c r="A67" s="165" t="s">
         <v>149</v>
       </c>
-      <c r="B67" s="164"/>
+      <c r="B67" s="166"/>
       <c r="C67" s="5"/>
-      <c r="D67" s="167">
+      <c r="D67" s="169">
         <v>190000</v>
       </c>
-      <c r="E67" s="169"/>
+      <c r="E67" s="171"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68" s="165"/>
-      <c r="B68" s="166"/>
+      <c r="A68" s="167"/>
+      <c r="B68" s="168"/>
       <c r="C68" s="61"/>
-      <c r="D68" s="168"/>
-      <c r="E68" s="170"/>
+      <c r="D68" s="170"/>
+      <c r="E68" s="172"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="58"/>
@@ -2500,7 +2508,7 @@
       </c>
       <c r="B75" s="97">
         <f>E63</f>
-        <v>3230136</v>
+        <v>3277470</v>
       </c>
       <c r="D75" s="51"/>
     </row>
@@ -2510,7 +2518,7 @@
       </c>
       <c r="B76" s="97">
         <f>E63-E61</f>
-        <v>2539509.59</v>
+        <v>2586843.59</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2534,25 +2542,25 @@
     <row r="79" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="162"/>
-      <c r="B81" s="162"/>
-      <c r="C81" s="162"/>
-      <c r="D81" s="162"/>
-      <c r="E81" s="162"/>
+      <c r="A81" s="164"/>
+      <c r="B81" s="164"/>
+      <c r="C81" s="164"/>
+      <c r="D81" s="164"/>
+      <c r="E81" s="164"/>
     </row>
     <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="162"/>
-      <c r="B82" s="162"/>
-      <c r="C82" s="162"/>
-      <c r="D82" s="162"/>
-      <c r="E82" s="162"/>
+      <c r="A82" s="164"/>
+      <c r="B82" s="164"/>
+      <c r="C82" s="164"/>
+      <c r="D82" s="164"/>
+      <c r="E82" s="164"/>
     </row>
     <row r="83" spans="1:5" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="162"/>
-      <c r="B83" s="162"/>
-      <c r="C83" s="162"/>
-      <c r="D83" s="162"/>
-      <c r="E83" s="162"/>
+      <c r="A83" s="164"/>
+      <c r="B83" s="164"/>
+      <c r="C83" s="164"/>
+      <c r="D83" s="164"/>
+      <c r="E83" s="164"/>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="23" t="s">
@@ -2610,7 +2618,7 @@
       </c>
       <c r="B91" s="55">
         <f>-B76</f>
-        <v>-2539509.59</v>
+        <v>-2586843.59</v>
       </c>
       <c r="C91" s="24"/>
     </row>
@@ -2630,7 +2638,7 @@
       </c>
       <c r="B93" s="132">
         <f>SUM(B86:B92)</f>
-        <v>-305170.77749999985</v>
+        <v>-352504.77749999985</v>
       </c>
       <c r="C93" s="27"/>
     </row>
@@ -2706,16 +2714,16 @@
     <row r="103" spans="1:13" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="104" spans="1:13" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="105" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A105" s="159" t="s">
+      <c r="A105" s="161" t="s">
         <v>56</v>
       </c>
-      <c r="B105" s="159"/>
-      <c r="C105" s="159"/>
+      <c r="B105" s="161"/>
+      <c r="C105" s="161"/>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A106" s="159"/>
-      <c r="B106" s="159"/>
-      <c r="C106" s="159"/>
+      <c r="A106" s="161"/>
+      <c r="B106" s="161"/>
+      <c r="C106" s="161"/>
     </row>
     <row r="107" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="63"/>
@@ -2743,32 +2751,32 @@
       <c r="M110" s="8"/>
     </row>
     <row r="111" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="158"/>
-      <c r="B111" s="158"/>
-      <c r="C111" s="158"/>
-      <c r="D111" s="158"/>
-      <c r="E111" s="158"/>
+      <c r="A111" s="160"/>
+      <c r="B111" s="160"/>
+      <c r="C111" s="160"/>
+      <c r="D111" s="160"/>
+      <c r="E111" s="160"/>
     </row>
     <row r="112" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="158"/>
-      <c r="B112" s="158"/>
-      <c r="C112" s="158"/>
-      <c r="D112" s="158"/>
-      <c r="E112" s="158"/>
+      <c r="A112" s="160"/>
+      <c r="B112" s="160"/>
+      <c r="C112" s="160"/>
+      <c r="D112" s="160"/>
+      <c r="E112" s="160"/>
     </row>
     <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="158"/>
-      <c r="B113" s="158"/>
-      <c r="C113" s="158"/>
-      <c r="D113" s="158"/>
-      <c r="E113" s="158"/>
+      <c r="A113" s="160"/>
+      <c r="B113" s="160"/>
+      <c r="C113" s="160"/>
+      <c r="D113" s="160"/>
+      <c r="E113" s="160"/>
     </row>
     <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="158"/>
-      <c r="B114" s="158"/>
-      <c r="C114" s="158"/>
-      <c r="D114" s="158"/>
-      <c r="E114" s="158"/>
+      <c r="A114" s="160"/>
+      <c r="B114" s="160"/>
+      <c r="C114" s="160"/>
+      <c r="D114" s="160"/>
+      <c r="E114" s="160"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -2824,18 +2832,18 @@
         <v>49</v>
       </c>
       <c r="E1" s="6"/>
-      <c r="F1" s="171" t="s">
+      <c r="F1" s="180" t="s">
         <v>108</v>
       </c>
-      <c r="G1" s="171"/>
-      <c r="H1" s="171"/>
-      <c r="I1" s="171"/>
-      <c r="J1" s="171"/>
-      <c r="K1" s="171"/>
-      <c r="L1" s="171"/>
-      <c r="M1" s="171"/>
-      <c r="N1" s="171"/>
-      <c r="O1" s="171"/>
+      <c r="G1" s="180"/>
+      <c r="H1" s="180"/>
+      <c r="I1" s="180"/>
+      <c r="J1" s="180"/>
+      <c r="K1" s="180"/>
+      <c r="L1" s="180"/>
+      <c r="M1" s="180"/>
+      <c r="N1" s="180"/>
+      <c r="O1" s="180"/>
       <c r="P1" s="6"/>
     </row>
     <row r="2" spans="1:19" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -2858,10 +2866,10 @@
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
-      <c r="O2" s="179">
+      <c r="O2" s="186">
         <v>2200000</v>
       </c>
-      <c r="P2" s="179"/>
+      <c r="P2" s="186"/>
       <c r="Q2" s="22"/>
     </row>
     <row r="3" spans="1:19" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -2883,80 +2891,80 @@
       </c>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
-      <c r="O3" s="180"/>
-      <c r="P3" s="180"/>
+      <c r="O3" s="187"/>
+      <c r="P3" s="187"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="184" t="s">
+      <c r="A4" s="175" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="186" t="s">
+      <c r="B4" s="177" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="174" t="s">
+      <c r="C4" s="173" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="174" t="s">
+      <c r="D4" s="173" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="174" t="s">
+      <c r="E4" s="173" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="174" t="s">
+      <c r="F4" s="173" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="174" t="s">
+      <c r="G4" s="173" t="s">
         <v>67</v>
       </c>
-      <c r="H4" s="174" t="s">
+      <c r="H4" s="173" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="174" t="s">
+      <c r="I4" s="173" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="176" t="s">
+      <c r="J4" s="183" t="s">
         <v>53</v>
       </c>
-      <c r="K4" s="172" t="s">
+      <c r="K4" s="181" t="s">
         <v>45</v>
       </c>
-      <c r="L4" s="172" t="s">
+      <c r="L4" s="181" t="s">
         <v>11</v>
       </c>
-      <c r="M4" s="172" t="s">
+      <c r="M4" s="181" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="172" t="s">
+      <c r="N4" s="181" t="s">
         <v>138</v>
       </c>
       <c r="O4" s="71" t="s">
         <v>64</v>
       </c>
-      <c r="P4" s="181" t="s">
+      <c r="P4" s="188" t="s">
         <v>63</v>
       </c>
       <c r="S4" s="51"/>
     </row>
     <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="185"/>
-      <c r="B5" s="187"/>
-      <c r="C5" s="175"/>
-      <c r="D5" s="175"/>
-      <c r="E5" s="183"/>
-      <c r="F5" s="175"/>
-      <c r="G5" s="175"/>
-      <c r="H5" s="175"/>
-      <c r="I5" s="183"/>
-      <c r="J5" s="177"/>
-      <c r="K5" s="173"/>
-      <c r="L5" s="178"/>
-      <c r="M5" s="173"/>
-      <c r="N5" s="173"/>
+      <c r="A5" s="176"/>
+      <c r="B5" s="178"/>
+      <c r="C5" s="179"/>
+      <c r="D5" s="179"/>
+      <c r="E5" s="174"/>
+      <c r="F5" s="179"/>
+      <c r="G5" s="179"/>
+      <c r="H5" s="179"/>
+      <c r="I5" s="174"/>
+      <c r="J5" s="184"/>
+      <c r="K5" s="182"/>
+      <c r="L5" s="185"/>
+      <c r="M5" s="182"/>
+      <c r="N5" s="182"/>
       <c r="O5" s="69" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 16/06</v>
       </c>
-      <c r="P5" s="182"/>
+      <c r="P5" s="189"/>
     </row>
     <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
@@ -4138,101 +4146,93 @@
     </row>
     <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="28" spans="1:20" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D28" s="158" t="s">
+      <c r="D28" s="160" t="s">
         <v>109</v>
       </c>
-      <c r="E28" s="158"/>
-      <c r="F28" s="158"/>
-      <c r="G28" s="158"/>
-      <c r="H28" s="158"/>
-      <c r="I28" s="158"/>
-      <c r="J28" s="158"/>
-      <c r="K28" s="158"/>
-      <c r="L28" s="158"/>
-      <c r="M28" s="158"/>
-      <c r="N28" s="158"/>
-      <c r="O28" s="158"/>
+      <c r="E28" s="160"/>
+      <c r="F28" s="160"/>
+      <c r="G28" s="160"/>
+      <c r="H28" s="160"/>
+      <c r="I28" s="160"/>
+      <c r="J28" s="160"/>
+      <c r="K28" s="160"/>
+      <c r="L28" s="160"/>
+      <c r="M28" s="160"/>
+      <c r="N28" s="160"/>
+      <c r="O28" s="160"/>
     </row>
     <row r="29" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D29" s="158"/>
-      <c r="E29" s="158"/>
-      <c r="F29" s="158"/>
-      <c r="G29" s="158"/>
-      <c r="H29" s="158"/>
-      <c r="I29" s="158"/>
-      <c r="J29" s="158"/>
-      <c r="K29" s="158"/>
-      <c r="L29" s="158"/>
-      <c r="M29" s="158"/>
-      <c r="N29" s="158"/>
-      <c r="O29" s="158"/>
+      <c r="D29" s="160"/>
+      <c r="E29" s="160"/>
+      <c r="F29" s="160"/>
+      <c r="G29" s="160"/>
+      <c r="H29" s="160"/>
+      <c r="I29" s="160"/>
+      <c r="J29" s="160"/>
+      <c r="K29" s="160"/>
+      <c r="L29" s="160"/>
+      <c r="M29" s="160"/>
+      <c r="N29" s="160"/>
+      <c r="O29" s="160"/>
     </row>
     <row r="30" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D30" s="158"/>
-      <c r="E30" s="158"/>
-      <c r="F30" s="158"/>
-      <c r="G30" s="158"/>
-      <c r="H30" s="158"/>
-      <c r="I30" s="158"/>
-      <c r="J30" s="158"/>
-      <c r="K30" s="158"/>
-      <c r="L30" s="158"/>
-      <c r="M30" s="158"/>
-      <c r="N30" s="158"/>
-      <c r="O30" s="158"/>
+      <c r="D30" s="160"/>
+      <c r="E30" s="160"/>
+      <c r="F30" s="160"/>
+      <c r="G30" s="160"/>
+      <c r="H30" s="160"/>
+      <c r="I30" s="160"/>
+      <c r="J30" s="160"/>
+      <c r="K30" s="160"/>
+      <c r="L30" s="160"/>
+      <c r="M30" s="160"/>
+      <c r="N30" s="160"/>
+      <c r="O30" s="160"/>
     </row>
     <row r="31" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D31" s="158"/>
-      <c r="E31" s="158"/>
-      <c r="F31" s="158"/>
-      <c r="G31" s="158"/>
-      <c r="H31" s="158"/>
-      <c r="I31" s="158"/>
-      <c r="J31" s="158"/>
-      <c r="K31" s="158"/>
-      <c r="L31" s="158"/>
-      <c r="M31" s="158"/>
-      <c r="N31" s="158"/>
-      <c r="O31" s="158"/>
+      <c r="D31" s="160"/>
+      <c r="E31" s="160"/>
+      <c r="F31" s="160"/>
+      <c r="G31" s="160"/>
+      <c r="H31" s="160"/>
+      <c r="I31" s="160"/>
+      <c r="J31" s="160"/>
+      <c r="K31" s="160"/>
+      <c r="L31" s="160"/>
+      <c r="M31" s="160"/>
+      <c r="N31" s="160"/>
+      <c r="O31" s="160"/>
     </row>
     <row r="32" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D32" s="158"/>
-      <c r="E32" s="158"/>
-      <c r="F32" s="158"/>
-      <c r="G32" s="158"/>
-      <c r="H32" s="158"/>
-      <c r="I32" s="158"/>
-      <c r="J32" s="158"/>
-      <c r="K32" s="158"/>
-      <c r="L32" s="158"/>
-      <c r="M32" s="158"/>
-      <c r="N32" s="158"/>
-      <c r="O32" s="158"/>
+      <c r="D32" s="160"/>
+      <c r="E32" s="160"/>
+      <c r="F32" s="160"/>
+      <c r="G32" s="160"/>
+      <c r="H32" s="160"/>
+      <c r="I32" s="160"/>
+      <c r="J32" s="160"/>
+      <c r="K32" s="160"/>
+      <c r="L32" s="160"/>
+      <c r="M32" s="160"/>
+      <c r="N32" s="160"/>
+      <c r="O32" s="160"/>
     </row>
     <row r="33" spans="4:15" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D33" s="158"/>
-      <c r="E33" s="158"/>
-      <c r="F33" s="158"/>
-      <c r="G33" s="158"/>
-      <c r="H33" s="158"/>
-      <c r="I33" s="158"/>
-      <c r="J33" s="158"/>
-      <c r="K33" s="158"/>
-      <c r="L33" s="158"/>
-      <c r="M33" s="158"/>
-      <c r="N33" s="158"/>
-      <c r="O33" s="158"/>
+      <c r="D33" s="160"/>
+      <c r="E33" s="160"/>
+      <c r="F33" s="160"/>
+      <c r="G33" s="160"/>
+      <c r="H33" s="160"/>
+      <c r="I33" s="160"/>
+      <c r="J33" s="160"/>
+      <c r="K33" s="160"/>
+      <c r="L33" s="160"/>
+      <c r="M33" s="160"/>
+      <c r="N33" s="160"/>
+      <c r="O33" s="160"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="D28:O33"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
     <mergeCell ref="F1:O1"/>
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="G4:G5"/>
@@ -4244,6 +4244,14 @@
     <mergeCell ref="O3:P3"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="N4:N5"/>
+    <mergeCell ref="D28:O33"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>

--- a/PUEYRREDON 1494/Mayo/PUEYRREDON MAYO.xlsx
+++ b/PUEYRREDON 1494/Mayo/PUEYRREDON MAYO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\PUEYRREDON 1494\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PUEYRREDON 1494\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7637B611-4A74-4DA7-BA27-459CB954B51B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A9E4A9E-1F40-4BC9-A1C7-6EB54CCFAFF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$110</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$109</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="158">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -387,9 +387,6 @@
     <t>Metrogas</t>
   </si>
   <si>
-    <t>ART DE LIMPIEZA</t>
-  </si>
-  <si>
     <t>Ben Ada</t>
   </si>
   <si>
@@ -414,9 +411,6 @@
     <t>Britez Nicolas</t>
   </si>
   <si>
-    <t>Gonzalo Emanuel</t>
-  </si>
-  <si>
     <t>Nahuel Cattani</t>
   </si>
   <si>
@@ -447,36 +441,15 @@
     <t>Mes de ABRIL</t>
   </si>
   <si>
-    <t>Seguro Vida colectivo personal de limpieza - Cuota 7/12</t>
-  </si>
-  <si>
-    <t>Debito 03/04</t>
-  </si>
-  <si>
-    <t>PMC 07/04</t>
-  </si>
-  <si>
-    <t>PMC 10/04</t>
-  </si>
-  <si>
-    <t>Debito 14/04</t>
-  </si>
-  <si>
     <t>PREVISION ORDINARIA</t>
   </si>
   <si>
     <t>Seguro Mercantil Andina - Poliza Nro. 001183277</t>
   </si>
   <si>
-    <t>Fotocopias - Administracion anterior</t>
-  </si>
-  <si>
     <t>Daniela Ferino</t>
   </si>
   <si>
-    <t>Cuota 2/9 arreglo terraza Sr. Luis (Total a abonar $1.250.000) - No se prorratea ya que se previsiono</t>
-  </si>
-  <si>
     <t>VTO 16/06</t>
   </si>
   <si>
@@ -489,27 +462,58 @@
     <t>Sindicatos mes de MAYO</t>
   </si>
   <si>
-    <t>Mantenimiento Ascensores -  Mes de ABRIL - No llego la factura</t>
-  </si>
-  <si>
-    <t>Tanques</t>
-  </si>
-  <si>
     <t>Camara de seguridad Imou Ipc-f22p-d</t>
+  </si>
+  <si>
+    <t>Debito 05/05</t>
+  </si>
+  <si>
+    <t>Tanque cuota 1 de 3 limpieza, recapeo, cambio de tapas</t>
+  </si>
+  <si>
+    <t>Transf 16/05</t>
+  </si>
+  <si>
+    <t>Debito 13/05</t>
+  </si>
+  <si>
+    <t>Mantenimiento Ascensores - Mes de ABRIL</t>
+  </si>
+  <si>
+    <t>Mantenimiento Ascensores - Mes de MAYO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seguro Vida colectivo personal de limpieza </t>
+  </si>
+  <si>
+    <t>Cuota 3/9 arreglo terraza Sr. Luis (Total a abonar $1.250.000) - No se prorratea ya que se previsiono</t>
+  </si>
+  <si>
+    <t>PMC 07/05</t>
+  </si>
+  <si>
+    <t>Gonzalo Emanuel Gonzalez</t>
+  </si>
+  <si>
+    <t>Maria Eugenia Mauturano</t>
+  </si>
+  <si>
+    <t>PMC 06/05</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+  <numFmts count="8">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="&quot;Bs&quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="&quot;Bs&quot;#,##0.00"/>
+    <numFmt numFmtId="170" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="27" x14ac:knownFonts="1">
     <font>
@@ -1139,11 +1143,11 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="191">
+  <cellXfs count="189">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1151,7 +1155,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1166,16 +1170,16 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
@@ -1187,8 +1191,8 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1198,39 +1202,37 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="9" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="14" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1244,8 +1246,8 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="10" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1253,18 +1255,18 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="16" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1275,81 +1277,77 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="10" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="22" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="10" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="10" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="10" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="10" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="7" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="10" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="25" fillId="8" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="25" fillId="8" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="23" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="23" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="23" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="23" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="23" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="26" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="7" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="26" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1389,10 +1387,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1401,9 +1399,42 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1419,40 +1450,15 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="21" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -1818,81 +1824,81 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M114"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M113"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="32"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="15"/>
-      <c r="B2" s="78" t="s">
+      <c r="B2" s="76" t="s">
         <v>112</v>
       </c>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="79"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="77"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="16"/>
-      <c r="B3" s="80" t="s">
+      <c r="B3" s="78" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="81"/>
-    </row>
-    <row r="4" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="79"/>
+    </row>
+    <row r="4" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="16"/>
-      <c r="B4" s="95" t="s">
+      <c r="B4" s="93" t="s">
         <v>110</v>
       </c>
-      <c r="C4" s="80"/>
-      <c r="D4" s="94" t="s">
+      <c r="C4" s="78"/>
+      <c r="D4" s="92" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="81"/>
-    </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E4" s="79"/>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="93" t="s">
+      <c r="B5" s="91" t="s">
         <v>65</v>
       </c>
       <c r="C5" s="20"/>
       <c r="D5" s="20"/>
       <c r="E5" s="21"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>111</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="C6" s="17"/>
-      <c r="D6" s="80" t="s">
+      <c r="D6" s="78" t="s">
         <v>52</v>
       </c>
       <c r="E6" s="18"/>
     </row>
-    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
         <v>107</v>
       </c>
@@ -1901,57 +1907,57 @@
       <c r="D7" s="20"/>
       <c r="E7" s="21"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="157" t="s">
-        <v>150</v>
-      </c>
-      <c r="C9" s="157"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="157"/>
-      <c r="C10" s="157"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="157"/>
-      <c r="C11" s="157"/>
-    </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="156" t="s">
-        <v>124</v>
-      </c>
-      <c r="B14" s="156"/>
-      <c r="C14" s="156"/>
-      <c r="D14" s="156"/>
-      <c r="E14" s="156"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="156"/>
-      <c r="B15" s="156"/>
-      <c r="C15" s="156"/>
-      <c r="D15" s="156"/>
-      <c r="E15" s="156"/>
-    </row>
-    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="156"/>
-      <c r="B16" s="156"/>
-      <c r="C16" s="156"/>
-      <c r="D16" s="156"/>
-      <c r="E16" s="156"/>
-    </row>
-    <row r="17" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="156"/>
-      <c r="B17" s="156"/>
-      <c r="C17" s="156"/>
-      <c r="D17" s="156"/>
-      <c r="E17" s="156"/>
-    </row>
-    <row r="18" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="151" t="s">
+        <v>141</v>
+      </c>
+      <c r="C9" s="151"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="151"/>
+      <c r="C10" s="151"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B11" s="151"/>
+      <c r="C11" s="151"/>
+    </row>
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="150" t="s">
+        <v>123</v>
+      </c>
+      <c r="B14" s="150"/>
+      <c r="C14" s="150"/>
+      <c r="D14" s="150"/>
+      <c r="E14" s="150"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="150"/>
+      <c r="B15" s="150"/>
+      <c r="C15" s="150"/>
+      <c r="D15" s="150"/>
+      <c r="E15" s="150"/>
+    </row>
+    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="150"/>
+      <c r="B16" s="150"/>
+      <c r="C16" s="150"/>
+      <c r="D16" s="150"/>
+      <c r="E16" s="150"/>
+    </row>
+    <row r="17" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="150"/>
+      <c r="B17" s="150"/>
+      <c r="C17" s="150"/>
+      <c r="D17" s="150"/>
+      <c r="E17" s="150"/>
+    </row>
+    <row r="18" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>23</v>
       </c>
@@ -1960,7 +1966,7 @@
       <c r="D21" s="9"/>
       <c r="E21" s="14"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="40" t="s">
         <v>59</v>
       </c>
@@ -1969,203 +1975,203 @@
       <c r="D22" s="38"/>
       <c r="E22" s="38"/>
     </row>
-    <row r="23" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>114</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
-      <c r="D23" s="143">
+      <c r="D23" s="139">
         <v>769441.8</v>
       </c>
-      <c r="E23" s="98"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E23" s="96"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>60</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
-      <c r="D24" s="143">
+      <c r="D24" s="139">
         <v>-168081.61</v>
       </c>
-      <c r="E24" s="98"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E24" s="96"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>62</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
-      <c r="D25" s="143">
+      <c r="D25" s="139">
         <v>0.81</v>
       </c>
-      <c r="E25" s="98"/>
+      <c r="E25" s="96"/>
       <c r="H25" s="22"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
-      <c r="D26" s="143"/>
-      <c r="E26" s="98"/>
+      <c r="D26" s="139"/>
+      <c r="E26" s="96"/>
       <c r="H26" s="5"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="67" t="s">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="65" t="s">
         <v>61</v>
       </c>
-      <c r="B27" s="67"/>
-      <c r="C27" s="67"/>
-      <c r="D27" s="144">
+      <c r="B27" s="65"/>
+      <c r="C27" s="65"/>
+      <c r="D27" s="140">
         <f>SUM(D23:D26)</f>
         <v>601361.00000000012</v>
       </c>
-      <c r="E27" s="99"/>
+      <c r="E27" s="97"/>
       <c r="H27" s="5"/>
     </row>
-    <row r="28" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="30" t="s">
         <v>1</v>
       </c>
       <c r="B28" s="30"/>
       <c r="C28" s="30"/>
-      <c r="D28" s="145"/>
-      <c r="E28" s="100">
+      <c r="D28" s="141"/>
+      <c r="E28" s="98">
         <f>D27</f>
         <v>601361.00000000012</v>
       </c>
       <c r="F28" s="22"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="40" t="s">
         <v>37</v>
       </c>
       <c r="B29" s="40"/>
       <c r="C29" s="40"/>
-      <c r="D29" s="146"/>
-      <c r="E29" s="101"/>
-    </row>
-    <row r="30" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="74" t="s">
-        <v>125</v>
+      <c r="D29" s="142"/>
+      <c r="E29" s="99"/>
+    </row>
+    <row r="30" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="72" t="s">
+        <v>124</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C30" s="5"/>
-      <c r="D30" s="143">
+      <c r="D30" s="139">
         <v>31000</v>
       </c>
-      <c r="E30" s="102"/>
-    </row>
-    <row r="31" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E30" s="100"/>
+    </row>
+    <row r="31" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>54</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="C31" s="5"/>
-      <c r="D31" s="143">
+      <c r="D31" s="139">
         <v>120000</v>
       </c>
-      <c r="E31" s="102"/>
-    </row>
-    <row r="32" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E31" s="100"/>
+    </row>
+    <row r="32" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="30" t="s">
         <v>33</v>
       </c>
       <c r="B32" s="30"/>
       <c r="C32" s="30"/>
-      <c r="D32" s="147"/>
-      <c r="E32" s="103">
+      <c r="D32" s="143"/>
+      <c r="E32" s="101">
         <f>SUM(D30:D31)</f>
         <v>151000</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="38" t="s">
         <v>55</v>
       </c>
       <c r="B33" s="39"/>
       <c r="C33" s="39"/>
-      <c r="D33" s="148"/>
-      <c r="E33" s="76"/>
-    </row>
-    <row r="34" spans="1:7" s="44" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="158" t="s">
-        <v>146</v>
-      </c>
-      <c r="B34" s="159"/>
+      <c r="D33" s="144"/>
+      <c r="E33" s="74"/>
+    </row>
+    <row r="34" spans="1:7" s="44" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="152" t="s">
+        <v>139</v>
+      </c>
+      <c r="B34" s="153"/>
       <c r="C34" s="63"/>
-      <c r="D34" s="149">
+      <c r="D34" s="145">
         <v>87562.7</v>
       </c>
-      <c r="E34" s="126"/>
-    </row>
-    <row r="35" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="158" t="s">
-        <v>140</v>
-      </c>
-      <c r="B35" s="159"/>
+      <c r="E34" s="124"/>
+    </row>
+    <row r="35" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="152" t="s">
+        <v>152</v>
+      </c>
+      <c r="B35" s="153"/>
       <c r="C35" s="63"/>
-      <c r="D35" s="150">
+      <c r="D35" s="146">
         <v>6646.91</v>
       </c>
-      <c r="E35" s="126"/>
-    </row>
-    <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E35" s="124"/>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="30" t="s">
         <v>2</v>
       </c>
       <c r="B36" s="30"/>
       <c r="C36" s="30"/>
-      <c r="D36" s="147"/>
-      <c r="E36" s="104">
+      <c r="D36" s="143"/>
+      <c r="E36" s="102">
         <f>SUM(D34:D35)</f>
         <v>94209.61</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="40" t="s">
         <v>34</v>
       </c>
       <c r="B37" s="31"/>
       <c r="C37" s="31"/>
-      <c r="D37" s="151"/>
-      <c r="E37" s="105"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D37" s="147"/>
+      <c r="E37" s="103"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>113</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="61"/>
-      <c r="D38" s="154">
+      <c r="D38" s="148">
         <v>371131.27</v>
       </c>
-      <c r="E38" s="129" t="s">
-        <v>143</v>
-      </c>
-      <c r="G38" s="124"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E38" s="125" t="s">
+        <v>157</v>
+      </c>
+      <c r="G38" s="122"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>116</v>
       </c>
       <c r="C39" s="5"/>
-      <c r="D39" s="154">
+      <c r="D39" s="148">
         <v>19236.05</v>
       </c>
-      <c r="E39" s="130" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E39" s="126" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="str">
         <f>A39</f>
         <v>Sindicatos mes de MAYO</v>
@@ -2174,15 +2180,15 @@
         <v>117</v>
       </c>
       <c r="C40" s="5"/>
-      <c r="D40" s="154">
+      <c r="D40" s="148">
         <v>62013.71</v>
       </c>
-      <c r="E40" s="130" t="str">
+      <c r="E40" s="126" t="str">
         <f>E39</f>
-        <v>Debito 14/04</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+        <v>Debito 13/05</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="str">
         <f>A40</f>
         <v>Sindicatos mes de MAYO</v>
@@ -2191,606 +2197,597 @@
         <v>118</v>
       </c>
       <c r="C41" s="5"/>
-      <c r="D41" s="154">
+      <c r="D41" s="148">
         <v>3847.21</v>
       </c>
-      <c r="E41" s="131" t="str">
+      <c r="E41" s="127" t="str">
         <f>E40</f>
-        <v>Debito 14/04</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>Debito 13/05</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="30" t="s">
         <v>3</v>
       </c>
       <c r="B42" s="31"/>
       <c r="C42" s="31"/>
-      <c r="D42" s="153"/>
-      <c r="E42" s="104">
+      <c r="D42" s="149"/>
+      <c r="E42" s="102">
         <f>SUM(D38:D41)</f>
         <v>456228.24000000005</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="40" t="s">
         <v>36</v>
       </c>
       <c r="B43" s="31"/>
       <c r="C43" s="31"/>
-      <c r="D43" s="151"/>
-      <c r="E43" s="105"/>
-    </row>
-    <row r="44" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="155" t="s">
-        <v>154</v>
+      <c r="D43" s="147"/>
+      <c r="E43" s="103"/>
+    </row>
+    <row r="44" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="61" t="s">
+        <v>150</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
-      <c r="D44" s="154">
+      <c r="D44" s="148">
         <v>33360</v>
       </c>
-      <c r="E44" s="109"/>
-    </row>
-    <row r="45" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="155" t="s">
-        <v>154</v>
+      <c r="E44" s="107" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="61" t="s">
+        <v>151</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
-      <c r="D45" s="154">
+      <c r="D45" s="148">
         <v>36700</v>
       </c>
-      <c r="E45" s="109"/>
-    </row>
-    <row r="46" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E45" s="107" t="s">
+        <v>148</v>
+      </c>
+      <c r="G45" s="130"/>
+    </row>
+    <row r="46" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>115</v>
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
-      <c r="D46" s="152">
-        <v>62862.53</v>
-      </c>
-      <c r="E46" s="109" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D46" s="148">
+        <v>67240.149999999994</v>
+      </c>
+      <c r="E46" s="107" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>119</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
-      <c r="D47" s="152">
-        <v>20802.73</v>
-      </c>
-      <c r="E47" s="109" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="155" t="s">
-        <v>155</v>
+      <c r="D47" s="148">
+        <v>25000</v>
+      </c>
+      <c r="E47" s="107" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="61" t="s">
+        <v>147</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
-      <c r="D48" s="154">
+      <c r="D48" s="148">
         <v>1000000</v>
       </c>
-      <c r="E48" s="109"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" s="162"/>
-      <c r="B49" s="163"/>
+      <c r="E48" s="107" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="156"/>
+      <c r="B49" s="157"/>
       <c r="C49" s="64"/>
-      <c r="D49" s="108"/>
-      <c r="E49" s="106"/>
-    </row>
-    <row r="50" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D49" s="106"/>
+      <c r="E49" s="104"/>
+    </row>
+    <row r="50" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="30" t="s">
         <v>4</v>
       </c>
       <c r="B50" s="30"/>
       <c r="C50" s="30"/>
-      <c r="D50" s="147"/>
-      <c r="E50" s="104">
+      <c r="D50" s="143"/>
+      <c r="E50" s="102">
         <f>SUM(D44:D49)</f>
-        <v>1153725.26</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1162300.1499999999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="40" t="s">
         <v>35</v>
       </c>
       <c r="B51" s="30"/>
       <c r="C51" s="30"/>
-      <c r="D51" s="147"/>
-      <c r="E51" s="107"/>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" s="65" t="s">
-        <v>120</v>
-      </c>
-      <c r="B52" s="65"/>
-      <c r="C52" s="66"/>
-      <c r="D52" s="152">
+      <c r="D51" s="143"/>
+      <c r="E51" s="105"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="61"/>
+      <c r="B52" s="5"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="42"/>
+      <c r="E52" s="104"/>
+    </row>
+    <row r="53" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="B53" s="40"/>
+      <c r="C53" s="40"/>
+      <c r="D53" s="38"/>
+      <c r="E53" s="109">
+        <f>SUM(D52:D52)</f>
         <v>0</v>
       </c>
-      <c r="E52" s="128"/>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="B53" s="5"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="152">
-        <v>2940</v>
-      </c>
-      <c r="E53" s="127"/>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54" s="61" t="s">
-        <v>156</v>
-      </c>
-      <c r="B54" s="5"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="190">
-        <v>47334</v>
-      </c>
-      <c r="E54" s="106"/>
-    </row>
-    <row r="55" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="B55" s="40"/>
-      <c r="C55" s="40"/>
-      <c r="D55" s="38"/>
-      <c r="E55" s="111">
-        <f>SUM(D52:D54)</f>
-        <v>50274</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="40" t="s">
+    </row>
+    <row r="54" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="B56" s="75"/>
-      <c r="C56" s="30"/>
-      <c r="D56" s="145"/>
-      <c r="E56" s="107"/>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" s="5" t="s">
+      <c r="B54" s="73"/>
+      <c r="C54" s="30"/>
+      <c r="D54" s="141"/>
+      <c r="E54" s="105"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B57" s="5"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="152">
-        <v>30963.48</v>
-      </c>
-      <c r="E57" s="112"/>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" s="5" t="s">
+      <c r="B55" s="5"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="148">
+        <v>47733.48</v>
+      </c>
+      <c r="E55" s="110"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="5" t="s">
         <v>58</v>
       </c>
+      <c r="B56" s="5"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="148">
+        <v>49082</v>
+      </c>
+      <c r="E56" s="108"/>
+    </row>
+    <row r="57" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="60" t="s">
+        <v>33</v>
+      </c>
+      <c r="B57" s="60"/>
+      <c r="C57" s="60"/>
+      <c r="D57" s="111"/>
+      <c r="E57" s="102">
+        <f>SUM(D55:D56)</f>
+        <v>96815.48000000001</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
-      <c r="D58" s="152">
-        <v>49082</v>
-      </c>
-      <c r="E58" s="110"/>
-    </row>
-    <row r="59" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="60" t="s">
-        <v>33</v>
-      </c>
-      <c r="B59" s="60"/>
-      <c r="C59" s="60"/>
+      <c r="D58" s="96"/>
+      <c r="E58" s="112"/>
+    </row>
+    <row r="59" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="B59" s="33"/>
+      <c r="C59" s="33"/>
       <c r="D59" s="113"/>
-      <c r="E59" s="104">
-        <f>SUM(D57:D58)</f>
-        <v>80045.48</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="5"/>
-      <c r="B60" s="5"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="98"/>
-      <c r="E60" s="114"/>
-    </row>
-    <row r="61" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="33" t="s">
+      <c r="E59" s="114"/>
+    </row>
+    <row r="60" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="1"/>
+      <c r="D60" s="115"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="51"/>
+    </row>
+    <row r="61" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B61" s="10"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="117"/>
+      <c r="E61" s="118">
+        <f>(SUM(E28:E59))</f>
+        <v>2561914.48</v>
+      </c>
+      <c r="F61" s="51"/>
+      <c r="G61" s="130"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D62" s="115"/>
+      <c r="E62" s="115"/>
+      <c r="G62" s="130"/>
+    </row>
+    <row r="63" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D63" s="115"/>
+      <c r="E63" s="115"/>
+    </row>
+    <row r="64" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B64" s="12"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="119"/>
+      <c r="E64" s="120"/>
+    </row>
+    <row r="65" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="159" t="s">
+        <v>153</v>
+      </c>
+      <c r="B65" s="160"/>
+      <c r="C65" s="5"/>
+      <c r="D65" s="163">
+        <v>181000</v>
+      </c>
+      <c r="E65" s="165"/>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="161"/>
+      <c r="B66" s="162"/>
+      <c r="C66" s="61"/>
+      <c r="D66" s="164"/>
+      <c r="E66" s="166"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="188" t="s">
         <v>145</v>
       </c>
-      <c r="B61" s="33"/>
-      <c r="C61" s="33"/>
-      <c r="D61" s="115"/>
-      <c r="E61" s="116">
-        <v>690626.40999999992</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="1"/>
-      <c r="D62" s="117"/>
-      <c r="E62" s="118"/>
-      <c r="F62" s="51"/>
-    </row>
-    <row r="63" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B63" s="10"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="119"/>
-      <c r="E63" s="120">
-        <f>(SUM(E28:E61))</f>
-        <v>3277470</v>
-      </c>
-      <c r="F63" s="51"/>
-      <c r="G63" s="134"/>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="D64" s="117"/>
-      <c r="E64" s="117"/>
-      <c r="G64" s="134"/>
-    </row>
-    <row r="65" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D65" s="117"/>
-      <c r="E65" s="117"/>
-    </row>
-    <row r="66" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B66" s="12"/>
-      <c r="C66" s="13"/>
-      <c r="D66" s="121"/>
-      <c r="E66" s="122"/>
-    </row>
-    <row r="67" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="165" t="s">
-        <v>149</v>
-      </c>
-      <c r="B67" s="166"/>
-      <c r="C67" s="5"/>
-      <c r="D67" s="169">
-        <v>190000</v>
-      </c>
-      <c r="E67" s="171"/>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68" s="167"/>
-      <c r="B68" s="168"/>
-      <c r="C68" s="61"/>
-      <c r="D68" s="170"/>
-      <c r="E68" s="172"/>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A69" s="58"/>
-      <c r="B69" s="57"/>
-      <c r="C69" s="57"/>
-      <c r="D69" s="68"/>
-      <c r="E69" s="68">
-        <f>SUM(D67:D68)</f>
-        <v>190000</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A71" s="33" t="s">
+      <c r="B67" s="157"/>
+      <c r="C67" s="61"/>
+      <c r="D67" s="42">
+        <v>47334</v>
+      </c>
+      <c r="E67" s="187"/>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="58"/>
+      <c r="B68" s="57"/>
+      <c r="C68" s="57"/>
+      <c r="D68" s="66"/>
+      <c r="E68" s="66">
+        <f>SUM(D65:D67)</f>
+        <v>228334</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="B71" s="33"/>
-      <c r="C71" s="33"/>
-      <c r="D71" s="34"/>
-      <c r="E71" s="135"/>
-    </row>
-    <row r="72" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="73" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="3" t="s">
+      <c r="B70" s="33"/>
+      <c r="C70" s="33"/>
+      <c r="D70" s="34"/>
+      <c r="E70" s="131"/>
+    </row>
+    <row r="71" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="72" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B73" s="10"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="4"/>
-      <c r="E73" s="77">
-        <f>E69+E71</f>
-        <v>190000</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="75" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="96" t="s">
+      <c r="B72" s="10"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="75">
+        <f>E68+E70</f>
+        <v>228334</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="74" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="94" t="s">
         <v>28</v>
       </c>
-      <c r="B75" s="97">
-        <f>E63</f>
-        <v>3277470</v>
-      </c>
-      <c r="D75" s="51"/>
-    </row>
-    <row r="76" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="96" t="s">
+      <c r="B74" s="95">
+        <f>E61</f>
+        <v>2561914.48</v>
+      </c>
+      <c r="D74" s="51"/>
+    </row>
+    <row r="75" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="94" t="s">
         <v>29</v>
       </c>
-      <c r="B76" s="97">
-        <f>E63-E61</f>
-        <v>2586843.59</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="96" t="s">
+      <c r="B75" s="95">
+        <f>E61-E59</f>
+        <v>2561914.48</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="94" t="s">
         <v>41</v>
       </c>
-      <c r="B77" s="97">
-        <f>E73-E71</f>
-        <v>190000</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="96" t="s">
+      <c r="B76" s="95">
+        <f>E72-E70</f>
+        <v>228334</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="94" t="s">
         <v>66</v>
       </c>
-      <c r="B78" s="97">
-        <f>E73</f>
-        <v>190000</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="164"/>
-      <c r="B81" s="164"/>
-      <c r="C81" s="164"/>
-      <c r="D81" s="164"/>
-      <c r="E81" s="164"/>
-    </row>
-    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="164"/>
-      <c r="B82" s="164"/>
-      <c r="C82" s="164"/>
-      <c r="D82" s="164"/>
-      <c r="E82" s="164"/>
-    </row>
-    <row r="83" spans="1:5" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="164"/>
-      <c r="B83" s="164"/>
-      <c r="C83" s="164"/>
-      <c r="D83" s="164"/>
-      <c r="E83" s="164"/>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A85" s="23" t="s">
+      <c r="B77" s="95">
+        <f>E72</f>
+        <v>228334</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="158"/>
+      <c r="B80" s="158"/>
+      <c r="C80" s="158"/>
+      <c r="D80" s="158"/>
+      <c r="E80" s="158"/>
+    </row>
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="158"/>
+      <c r="B81" s="158"/>
+      <c r="C81" s="158"/>
+      <c r="D81" s="158"/>
+      <c r="E81" s="158"/>
+    </row>
+    <row r="82" spans="1:5" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="158"/>
+      <c r="B82" s="158"/>
+      <c r="C82" s="158"/>
+      <c r="D82" s="158"/>
+      <c r="E82" s="158"/>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="B85" s="46"/>
-      <c r="C85" s="24"/>
-    </row>
-    <row r="86" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="36" t="s">
+      <c r="B84" s="46"/>
+      <c r="C84" s="24"/>
+    </row>
+    <row r="85" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="B86" s="133">
-        <v>549424.81250000023</v>
-      </c>
-      <c r="C86" s="26"/>
-    </row>
-    <row r="87" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B85" s="129">
+        <v>724965.22249999992</v>
+      </c>
+      <c r="C85" s="26"/>
+    </row>
+    <row r="86" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="25" t="s">
+        <v>106</v>
+      </c>
+      <c r="B86" s="47">
+        <f>PRORRATEO!H25</f>
+        <v>1915682.4999999998</v>
+      </c>
+      <c r="C86" s="24"/>
+    </row>
+    <row r="87" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="25" t="s">
-        <v>106</v>
-      </c>
-      <c r="B87" s="47">
-        <f>PRORRATEO!H25</f>
-        <v>1874914</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="B87" s="55"/>
       <c r="C87" s="24"/>
     </row>
-    <row r="88" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="25" t="s">
-        <v>136</v>
+    <row r="88" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="135" t="s">
+        <v>135</v>
       </c>
       <c r="B88" s="55"/>
       <c r="C88" s="24"/>
     </row>
-    <row r="89" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="139" t="s">
-        <v>137</v>
-      </c>
-      <c r="B89" s="55"/>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="B89" s="108">
+        <f>B108</f>
+        <v>0</v>
+      </c>
       <c r="C89" s="24"/>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A90" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="B90" s="110">
-        <f>B109</f>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="B90" s="55">
+        <f>-B75</f>
+        <v>-2561914.48</v>
+      </c>
+      <c r="C90" s="24"/>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="B91" s="55">
+        <f>-(B76)</f>
+        <v>-228334</v>
+      </c>
+      <c r="C91" s="24"/>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="B92" s="128">
+        <f>SUM(B85:B91)</f>
+        <v>-149600.7575000003</v>
+      </c>
+      <c r="C92" s="27"/>
+    </row>
+    <row r="93" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B93" s="48"/>
+      <c r="C93" s="27"/>
+      <c r="D93" s="51"/>
+    </row>
+    <row r="94" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B94" s="49"/>
+      <c r="C94" s="27"/>
+    </row>
+    <row r="95" spans="1:5" s="44" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95"/>
+      <c r="B95" s="48"/>
+      <c r="C95" s="43"/>
+    </row>
+    <row r="96" spans="1:5" s="44" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="B96" s="41"/>
+      <c r="C96" s="43"/>
+      <c r="D96" s="54"/>
+    </row>
+    <row r="97" spans="1:13" s="44" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B97" s="42">
         <v>0</v>
       </c>
-      <c r="C90" s="24"/>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A91" s="45" t="s">
+      <c r="C97" s="43"/>
+    </row>
+    <row r="98" spans="1:13" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B98" s="41">
+        <v>0</v>
+      </c>
+      <c r="C98" s="27"/>
+      <c r="D98" s="51"/>
+    </row>
+    <row r="99" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="B91" s="55">
-        <f>-B76</f>
-        <v>-2586843.59</v>
-      </c>
-      <c r="C91" s="24"/>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A92" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="B92" s="55">
-        <f>-(B77)</f>
-        <v>-190000</v>
-      </c>
-      <c r="C92" s="24"/>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A93" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="B93" s="132">
-        <f>SUM(B86:B92)</f>
-        <v>-352504.77749999985</v>
-      </c>
-      <c r="C93" s="27"/>
-    </row>
-    <row r="94" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B94" s="48"/>
-      <c r="C94" s="27"/>
-      <c r="D94" s="51"/>
-    </row>
-    <row r="95" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B95" s="49"/>
-      <c r="C95" s="27"/>
-    </row>
-    <row r="96" spans="1:5" s="44" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96"/>
-      <c r="B96" s="48"/>
-      <c r="C96" s="43"/>
-    </row>
-    <row r="97" spans="1:13" s="44" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="B97" s="41"/>
-      <c r="C97" s="43"/>
-      <c r="D97" s="54"/>
-    </row>
-    <row r="98" spans="1:13" s="44" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B98" s="42">
-        <v>0</v>
-      </c>
-      <c r="C98" s="43"/>
-    </row>
-    <row r="99" spans="1:13" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="5" t="s">
-        <v>24</v>
       </c>
       <c r="B99" s="41">
         <v>0</v>
       </c>
       <c r="C99" s="27"/>
-      <c r="D99" s="51"/>
-    </row>
-    <row r="100" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="100" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B100" s="41">
         <v>0</v>
       </c>
-      <c r="C100" s="27"/>
-    </row>
-    <row r="101" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B101" s="41">
+      <c r="C100" s="29"/>
+    </row>
+    <row r="101" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="B101" s="56">
+        <f>SUM(B97:B100)</f>
         <v>0</v>
       </c>
-      <c r="C101" s="29"/>
-    </row>
-    <row r="102" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="B102" s="56">
-        <f>SUM(B98:B101)</f>
-        <v>0</v>
-      </c>
-      <c r="C102" s="24"/>
-    </row>
-    <row r="103" spans="1:13" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="104" spans="1:13" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A105" s="161" t="s">
+      <c r="C101" s="24"/>
+    </row>
+    <row r="102" spans="1:13" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="1:13" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A104" s="155" t="s">
         <v>56</v>
       </c>
-      <c r="B105" s="161"/>
-      <c r="C105" s="161"/>
-    </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A106" s="161"/>
-      <c r="B106" s="161"/>
-      <c r="C106" s="161"/>
-    </row>
-    <row r="107" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B104" s="155"/>
+      <c r="C104" s="155"/>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A105" s="155"/>
+      <c r="B105" s="155"/>
+      <c r="C105" s="155"/>
+    </row>
+    <row r="106" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="63"/>
+      <c r="B106" s="41"/>
+      <c r="C106" s="41">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="63"/>
       <c r="B107" s="41"/>
-      <c r="C107" s="41">
-        <v>40000</v>
-      </c>
-    </row>
-    <row r="108" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="63"/>
-      <c r="B108" s="41"/>
-      <c r="C108" s="123"/>
-    </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A109" s="52" t="s">
+      <c r="C107" s="121"/>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A108" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="B109" s="125">
-        <f>SUM(B107:B108)</f>
+      <c r="B108" s="123">
+        <f>SUM(B106:B107)</f>
         <v>0</v>
       </c>
-      <c r="C109" s="53"/>
-    </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M110" s="8"/>
-    </row>
-    <row r="111" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="160"/>
-      <c r="B111" s="160"/>
-      <c r="C111" s="160"/>
-      <c r="D111" s="160"/>
-      <c r="E111" s="160"/>
-    </row>
-    <row r="112" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="160"/>
-      <c r="B112" s="160"/>
-      <c r="C112" s="160"/>
-      <c r="D112" s="160"/>
-      <c r="E112" s="160"/>
-    </row>
-    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="160"/>
-      <c r="B113" s="160"/>
-      <c r="C113" s="160"/>
-      <c r="D113" s="160"/>
-      <c r="E113" s="160"/>
-    </row>
-    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="160"/>
-      <c r="B114" s="160"/>
-      <c r="C114" s="160"/>
-      <c r="D114" s="160"/>
-      <c r="E114" s="160"/>
+      <c r="C108" s="53"/>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M109" s="8"/>
+    </row>
+    <row r="110" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="154"/>
+      <c r="B110" s="154"/>
+      <c r="C110" s="154"/>
+      <c r="D110" s="154"/>
+      <c r="E110" s="154"/>
+    </row>
+    <row r="111" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="154"/>
+      <c r="B111" s="154"/>
+      <c r="C111" s="154"/>
+      <c r="D111" s="154"/>
+      <c r="E111" s="154"/>
+    </row>
+    <row r="112" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="154"/>
+      <c r="B112" s="154"/>
+      <c r="C112" s="154"/>
+      <c r="D112" s="154"/>
+      <c r="E112" s="154"/>
+    </row>
+    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="154"/>
+      <c r="B113" s="154"/>
+      <c r="C113" s="154"/>
+      <c r="D113" s="154"/>
+      <c r="E113" s="154"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A14:E17"/>
     <mergeCell ref="B9:C11"/>
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A111:E114"/>
-    <mergeCell ref="A105:C106"/>
+    <mergeCell ref="A110:E113"/>
+    <mergeCell ref="A104:C105"/>
     <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A81:E83"/>
-    <mergeCell ref="A67:B68"/>
-    <mergeCell ref="D67:D68"/>
-    <mergeCell ref="E67:E68"/>
+    <mergeCell ref="A80:E82"/>
+    <mergeCell ref="A65:B66"/>
+    <mergeCell ref="D65:D66"/>
+    <mergeCell ref="E65:E66"/>
+    <mergeCell ref="A67:B67"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2801,30 +2798,30 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:T33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5546875" customWidth="1"/>
-    <col min="3" max="3" width="6.88671875" customWidth="1"/>
-    <col min="4" max="4" width="18.5546875" customWidth="1"/>
-    <col min="5" max="5" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.109375" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" customWidth="1"/>
-    <col min="9" max="9" width="7.6640625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" customWidth="1"/>
-    <col min="11" max="11" width="9.88671875" customWidth="1"/>
-    <col min="12" max="12" width="11.33203125" customWidth="1"/>
-    <col min="13" max="13" width="10.5546875" customWidth="1"/>
-    <col min="14" max="14" width="10.5546875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5703125" customWidth="1"/>
+    <col min="3" max="3" width="6.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" customWidth="1"/>
+    <col min="12" max="12" width="11.28515625" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" customWidth="1"/>
+    <col min="14" max="14" width="10.5703125" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="14" customWidth="1"/>
-    <col min="16" max="16" width="14.109375" customWidth="1"/>
-    <col min="17" max="17" width="7.44140625" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" customWidth="1"/>
+    <col min="17" max="17" width="7.42578125" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -2832,21 +2829,21 @@
         <v>49</v>
       </c>
       <c r="E1" s="6"/>
-      <c r="F1" s="180" t="s">
+      <c r="F1" s="167" t="s">
         <v>108</v>
       </c>
-      <c r="G1" s="180"/>
-      <c r="H1" s="180"/>
-      <c r="I1" s="180"/>
-      <c r="J1" s="180"/>
-      <c r="K1" s="180"/>
-      <c r="L1" s="180"/>
-      <c r="M1" s="180"/>
-      <c r="N1" s="180"/>
-      <c r="O1" s="180"/>
+      <c r="G1" s="167"/>
+      <c r="H1" s="167"/>
+      <c r="I1" s="167"/>
+      <c r="J1" s="167"/>
+      <c r="K1" s="167"/>
+      <c r="L1" s="167"/>
+      <c r="M1" s="167"/>
+      <c r="N1" s="167"/>
+      <c r="O1" s="167"/>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:19" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -2866,13 +2863,14 @@
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
-      <c r="O2" s="186">
-        <v>2200000</v>
-      </c>
-      <c r="P2" s="186"/>
+      <c r="O2" s="175">
+        <f>T4</f>
+        <v>2609248.48</v>
+      </c>
+      <c r="P2" s="175"/>
       <c r="Q2" s="22"/>
     </row>
-    <row r="3" spans="1:19" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -2891,195 +2889,204 @@
       </c>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
-      <c r="O3" s="187"/>
-      <c r="P3" s="187"/>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="175" t="s">
+      <c r="O3" s="176">
+        <f>S6</f>
+        <v>47334</v>
+      </c>
+      <c r="P3" s="176"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="180" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="177" t="s">
+      <c r="B4" s="182" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="173" t="s">
+      <c r="C4" s="170" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="173" t="s">
+      <c r="D4" s="170" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="173" t="s">
+      <c r="E4" s="170" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="173" t="s">
+      <c r="F4" s="170" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="173" t="s">
+      <c r="G4" s="170" t="s">
         <v>67</v>
       </c>
-      <c r="H4" s="173" t="s">
+      <c r="H4" s="170" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="173" t="s">
+      <c r="I4" s="170" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="183" t="s">
+      <c r="J4" s="172" t="s">
         <v>53</v>
       </c>
-      <c r="K4" s="181" t="s">
+      <c r="K4" s="168" t="s">
         <v>45</v>
       </c>
-      <c r="L4" s="181" t="s">
+      <c r="L4" s="168" t="s">
         <v>11</v>
       </c>
-      <c r="M4" s="181" t="s">
+      <c r="M4" s="168" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="181" t="s">
-        <v>138</v>
-      </c>
-      <c r="O4" s="71" t="s">
+      <c r="N4" s="168" t="s">
+        <v>136</v>
+      </c>
+      <c r="O4" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="P4" s="188" t="s">
+      <c r="P4" s="177" t="s">
         <v>63</v>
       </c>
       <c r="S4" s="51"/>
-    </row>
-    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="176"/>
-      <c r="B5" s="178"/>
-      <c r="C5" s="179"/>
-      <c r="D5" s="179"/>
-      <c r="E5" s="174"/>
-      <c r="F5" s="179"/>
-      <c r="G5" s="179"/>
-      <c r="H5" s="179"/>
-      <c r="I5" s="174"/>
-      <c r="J5" s="184"/>
-      <c r="K5" s="182"/>
-      <c r="L5" s="185"/>
-      <c r="M5" s="182"/>
-      <c r="N5" s="182"/>
-      <c r="O5" s="69" t="str">
+      <c r="T4">
+        <v>2609248.48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="181"/>
+      <c r="B5" s="183"/>
+      <c r="C5" s="171"/>
+      <c r="D5" s="171"/>
+      <c r="E5" s="179"/>
+      <c r="F5" s="171"/>
+      <c r="G5" s="171"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="179"/>
+      <c r="J5" s="173"/>
+      <c r="K5" s="169"/>
+      <c r="L5" s="174"/>
+      <c r="M5" s="169"/>
+      <c r="N5" s="169"/>
+      <c r="O5" s="67" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 16/06</v>
       </c>
-      <c r="P5" s="189"/>
-    </row>
-    <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P5" s="178"/>
+    </row>
+    <row r="6" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="72">
+      <c r="B6" s="70">
         <v>1</v>
       </c>
-      <c r="C6" s="72" t="s">
+      <c r="C6" s="70" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="72" t="s">
+      <c r="D6" s="70" t="s">
         <v>71</v>
       </c>
-      <c r="E6" s="72" t="s">
-        <v>126</v>
-      </c>
-      <c r="F6" s="82">
+      <c r="E6" s="70" t="s">
+        <v>125</v>
+      </c>
+      <c r="F6" s="80">
         <v>3</v>
       </c>
-      <c r="G6" s="83">
-        <v>60000</v>
-      </c>
-      <c r="H6" s="84">
+      <c r="G6" s="184">
+        <v>66000.100000000006</v>
+      </c>
+      <c r="H6" s="185">
         <f>G6</f>
-        <v>60000</v>
-      </c>
-      <c r="I6" s="85"/>
-      <c r="J6" s="140">
+        <v>66000.100000000006</v>
+      </c>
+      <c r="I6" s="83"/>
+      <c r="J6" s="136">
         <f t="shared" ref="J6:J24" si="0">G6-H6</f>
         <v>0</v>
       </c>
-      <c r="K6" s="86">
+      <c r="K6" s="84">
         <f>IF(J6&gt;0,J6*5%,0)</f>
         <v>0</v>
       </c>
-      <c r="L6" s="87">
+      <c r="L6" s="85">
         <f t="shared" ref="L6:L24" si="1">O$3*F6%</f>
-        <v>0</v>
-      </c>
-      <c r="M6" s="87">
+        <v>1420.02</v>
+      </c>
+      <c r="M6" s="85">
         <f t="shared" ref="M6:M24" si="2">O$2*F6%</f>
-        <v>66000</v>
-      </c>
-      <c r="N6" s="136">
+        <v>78277.454400000002</v>
+      </c>
+      <c r="N6" s="132">
         <f>SUM(J6:M6)</f>
-        <v>66000</v>
-      </c>
-      <c r="O6" s="141" t="str">
+        <v>79697.474400000006</v>
+      </c>
+      <c r="O6" s="137" t="str">
         <f>CONCATENATE("$",ROUND(N6,0), ",", Q6)</f>
-        <v>$66000,1</v>
-      </c>
-      <c r="P6" s="142" t="str">
+        <v>$79697,1</v>
+      </c>
+      <c r="P6" s="138" t="str">
         <f>CONCATENATE("$",ROUND(N6*3%+ N6,0), ",", Q6)</f>
-        <v>$67980,1</v>
+        <v>$82088,1</v>
       </c>
       <c r="Q6" s="51" t="str">
         <f t="shared" ref="Q6:Q13" si="3">CONCATENATE(B6)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S6">
+        <v>47334</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="72">
+      <c r="B7" s="70">
         <v>2</v>
       </c>
-      <c r="C7" s="72" t="s">
+      <c r="C7" s="70" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="72" t="s">
+      <c r="D7" s="70" t="s">
         <v>73</v>
       </c>
-      <c r="E7" s="72" t="s">
-        <v>148</v>
-      </c>
-      <c r="F7" s="82">
+      <c r="E7" s="70" t="s">
+        <v>140</v>
+      </c>
+      <c r="F7" s="80">
         <v>3.8</v>
       </c>
-      <c r="G7" s="83">
-        <v>76000</v>
-      </c>
-      <c r="H7" s="84">
+      <c r="G7" s="184">
+        <v>83600.2</v>
+      </c>
+      <c r="H7" s="185">
         <f>G7</f>
-        <v>76000</v>
-      </c>
-      <c r="I7" s="85"/>
-      <c r="J7" s="140">
+        <v>83600.2</v>
+      </c>
+      <c r="I7" s="83"/>
+      <c r="J7" s="136">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K7" s="86">
+      <c r="K7" s="84">
         <f t="shared" ref="K7:K24" si="4">IF(J7&gt;0,J7*5%,0)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="87">
+      <c r="L7" s="85">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M7" s="87">
+        <v>1798.692</v>
+      </c>
+      <c r="M7" s="85">
         <f t="shared" si="2"/>
-        <v>83600</v>
-      </c>
-      <c r="N7" s="136">
+        <v>99151.442240000004</v>
+      </c>
+      <c r="N7" s="132">
         <f t="shared" ref="N7:N24" si="5">SUM(J7:M7)</f>
-        <v>83600</v>
-      </c>
-      <c r="O7" s="138" t="str">
+        <v>100950.13424</v>
+      </c>
+      <c r="O7" s="134" t="str">
         <f t="shared" ref="O7:O24" si="6">CONCATENATE("$",ROUND(N7,0), ",", Q7)</f>
-        <v>$83600,2</v>
-      </c>
-      <c r="P7" s="142" t="str">
+        <v>$100950,2</v>
+      </c>
+      <c r="P7" s="138" t="str">
         <f t="shared" ref="P7:P24" si="7">CONCATENATE("$",ROUND(N7*3%+ N7,0), ",", Q7)</f>
-        <v>$86108,2</v>
+        <v>$103979,2</v>
       </c>
       <c r="Q7" s="51" t="str">
         <f t="shared" si="3"/>
@@ -3087,120 +3094,117 @@
       </c>
       <c r="R7" s="51"/>
     </row>
-    <row r="8" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="72">
+      <c r="B8" s="70">
         <v>3</v>
       </c>
-      <c r="C8" s="72" t="s">
+      <c r="C8" s="70" t="s">
         <v>74</v>
       </c>
-      <c r="D8" s="72" t="s">
+      <c r="D8" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="E8" s="72" t="s">
-        <v>133</v>
-      </c>
-      <c r="F8" s="82">
+      <c r="E8" s="70" t="s">
+        <v>131</v>
+      </c>
+      <c r="F8" s="80">
         <v>3</v>
       </c>
-      <c r="G8" s="83">
-        <v>60000</v>
-      </c>
-      <c r="H8" s="84">
+      <c r="G8" s="184">
+        <v>66000.3</v>
+      </c>
+      <c r="H8" s="185">
         <f>G8</f>
-        <v>60000</v>
-      </c>
-      <c r="I8" s="85"/>
-      <c r="J8" s="140">
+        <v>66000.3</v>
+      </c>
+      <c r="I8" s="83"/>
+      <c r="J8" s="136">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K8" s="86">
+      <c r="K8" s="84">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L8" s="87">
+      <c r="L8" s="85">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M8" s="87">
+        <v>1420.02</v>
+      </c>
+      <c r="M8" s="85">
         <f t="shared" si="2"/>
-        <v>66000</v>
-      </c>
-      <c r="N8" s="136">
+        <v>78277.454400000002</v>
+      </c>
+      <c r="N8" s="132">
         <f t="shared" si="5"/>
-        <v>66000</v>
-      </c>
-      <c r="O8" s="138" t="str">
+        <v>79697.474400000006</v>
+      </c>
+      <c r="O8" s="134" t="str">
         <f t="shared" si="6"/>
-        <v>$66000,3</v>
-      </c>
-      <c r="P8" s="142" t="str">
+        <v>$79697,3</v>
+      </c>
+      <c r="P8" s="138" t="str">
         <f t="shared" si="7"/>
-        <v>$67980,3</v>
+        <v>$82088,3</v>
       </c>
       <c r="Q8" s="51" t="str">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="72">
+      <c r="B9" s="70">
         <v>4</v>
       </c>
-      <c r="C9" s="72" t="s">
+      <c r="C9" s="70" t="s">
         <v>76</v>
       </c>
-      <c r="D9" s="72" t="s">
+      <c r="D9" s="70" t="s">
         <v>77</v>
       </c>
-      <c r="E9" s="72" t="s">
-        <v>132</v>
-      </c>
-      <c r="F9" s="82">
+      <c r="E9" s="70" t="s">
+        <v>130</v>
+      </c>
+      <c r="F9" s="80">
         <v>3.1</v>
       </c>
-      <c r="G9" s="83">
-        <v>192610</v>
-      </c>
-      <c r="H9" s="84">
-        <f>20000*2+58400+20000</f>
-        <v>118400</v>
-      </c>
-      <c r="I9" s="85"/>
-      <c r="J9" s="140">
+      <c r="G9" s="184">
+        <v>146121.4</v>
+      </c>
+      <c r="H9" s="185"/>
+      <c r="I9" s="83"/>
+      <c r="J9" s="136">
         <f t="shared" si="0"/>
-        <v>74210</v>
-      </c>
-      <c r="K9" s="86">
+        <v>146121.4</v>
+      </c>
+      <c r="K9" s="84">
         <f t="shared" si="4"/>
-        <v>3710.5</v>
-      </c>
-      <c r="L9" s="87">
+        <v>7306.07</v>
+      </c>
+      <c r="L9" s="85">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M9" s="87">
+        <v>1467.354</v>
+      </c>
+      <c r="M9" s="85">
         <f t="shared" si="2"/>
-        <v>68200</v>
-      </c>
-      <c r="N9" s="136">
+        <v>80886.702879999997</v>
+      </c>
+      <c r="N9" s="132">
         <f t="shared" si="5"/>
-        <v>146120.5</v>
-      </c>
-      <c r="O9" s="138" t="str">
+        <v>235781.52687999999</v>
+      </c>
+      <c r="O9" s="134" t="str">
         <f t="shared" si="6"/>
-        <v>$146121,4</v>
-      </c>
-      <c r="P9" s="142" t="str">
+        <v>$235782,4</v>
+      </c>
+      <c r="P9" s="138" t="str">
         <f t="shared" si="7"/>
-        <v>$150504,4</v>
+        <v>$242855,4</v>
       </c>
       <c r="Q9" s="51" t="str">
         <f t="shared" si="3"/>
@@ -3208,57 +3212,57 @@
       </c>
       <c r="S9" s="51"/>
     </row>
-    <row r="10" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="72">
+      <c r="B10" s="70">
         <v>5</v>
       </c>
-      <c r="C10" s="72" t="s">
+      <c r="C10" s="70" t="s">
         <v>78</v>
       </c>
-      <c r="D10" s="72" t="s">
+      <c r="D10" s="70" t="s">
         <v>79</v>
       </c>
-      <c r="E10" s="72" t="s">
-        <v>134</v>
-      </c>
-      <c r="F10" s="82">
+      <c r="E10" s="70" t="s">
+        <v>132</v>
+      </c>
+      <c r="F10" s="80">
         <v>3.1</v>
       </c>
-      <c r="G10" s="83">
-        <v>56218</v>
-      </c>
-      <c r="H10" s="84"/>
-      <c r="I10" s="85"/>
-      <c r="J10" s="140">
+      <c r="G10" s="184">
+        <v>127229.5</v>
+      </c>
+      <c r="H10" s="185"/>
+      <c r="I10" s="83"/>
+      <c r="J10" s="136">
         <f t="shared" si="0"/>
-        <v>56218</v>
-      </c>
-      <c r="K10" s="86">
+        <v>127229.5</v>
+      </c>
+      <c r="K10" s="84">
         <f t="shared" si="4"/>
-        <v>2810.9</v>
-      </c>
-      <c r="L10" s="87">
+        <v>6361.4750000000004</v>
+      </c>
+      <c r="L10" s="85">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M10" s="87">
+        <v>1467.354</v>
+      </c>
+      <c r="M10" s="85">
         <f t="shared" si="2"/>
-        <v>68200</v>
-      </c>
-      <c r="N10" s="136">
+        <v>80886.702879999997</v>
+      </c>
+      <c r="N10" s="132">
         <f t="shared" si="5"/>
-        <v>127228.9</v>
-      </c>
-      <c r="O10" s="138" t="str">
+        <v>215945.03187999999</v>
+      </c>
+      <c r="O10" s="134" t="str">
         <f t="shared" si="6"/>
-        <v>$127229,5</v>
-      </c>
-      <c r="P10" s="142" t="str">
+        <v>$215945,5</v>
+      </c>
+      <c r="P10" s="138" t="str">
         <f t="shared" si="7"/>
-        <v>$131046,5</v>
+        <v>$222423,5</v>
       </c>
       <c r="Q10" s="51" t="str">
         <f t="shared" si="3"/>
@@ -3266,647 +3270,645 @@
       </c>
       <c r="S10" s="51"/>
     </row>
-    <row r="11" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="72">
+      <c r="B11" s="70">
         <v>6</v>
       </c>
-      <c r="C11" s="72" t="s">
+      <c r="C11" s="70" t="s">
         <v>80</v>
       </c>
-      <c r="D11" s="72" t="s">
+      <c r="D11" s="70" t="s">
         <v>81</v>
       </c>
-      <c r="E11" s="72"/>
-      <c r="F11" s="82">
+      <c r="E11" s="70"/>
+      <c r="F11" s="80">
         <v>3.2</v>
       </c>
-      <c r="G11" s="83">
-        <v>61594</v>
-      </c>
-      <c r="H11" s="84">
-        <f t="shared" ref="H11:H17" si="8">G11</f>
-        <v>61594</v>
-      </c>
-      <c r="I11" s="85"/>
-      <c r="J11" s="140">
+      <c r="G11" s="184">
+        <v>70400.600000000006</v>
+      </c>
+      <c r="H11" s="185">
+        <v>74400</v>
+      </c>
+      <c r="I11" s="83"/>
+      <c r="J11" s="136">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="86">
+        <v>-3999.3999999999942</v>
+      </c>
+      <c r="K11" s="84">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L11" s="87">
+      <c r="L11" s="85">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M11" s="87">
+        <v>1514.6880000000001</v>
+      </c>
+      <c r="M11" s="85">
         <f t="shared" si="2"/>
-        <v>70400</v>
-      </c>
-      <c r="N11" s="136">
+        <v>83495.951360000006</v>
+      </c>
+      <c r="N11" s="132">
         <f t="shared" si="5"/>
-        <v>70400</v>
-      </c>
-      <c r="O11" s="138" t="str">
+        <v>81011.239360000007</v>
+      </c>
+      <c r="O11" s="134" t="str">
         <f t="shared" si="6"/>
-        <v>$70400,6</v>
-      </c>
-      <c r="P11" s="142" t="str">
+        <v>$81011,6</v>
+      </c>
+      <c r="P11" s="138" t="str">
         <f t="shared" si="7"/>
-        <v>$72512,6</v>
+        <v>$83442,6</v>
       </c>
       <c r="Q11" s="51" t="str">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="72">
+      <c r="B12" s="70">
         <v>7</v>
       </c>
-      <c r="C12" s="72" t="s">
+      <c r="C12" s="70" t="s">
         <v>82</v>
       </c>
-      <c r="D12" s="72" t="s">
+      <c r="D12" s="70" t="s">
         <v>83</v>
       </c>
-      <c r="E12" s="72" t="s">
-        <v>127</v>
-      </c>
-      <c r="F12" s="82">
+      <c r="E12" s="70" t="s">
+        <v>126</v>
+      </c>
+      <c r="F12" s="80">
         <v>3.3</v>
       </c>
-      <c r="G12" s="83">
-        <v>66000</v>
-      </c>
-      <c r="H12" s="84">
-        <f t="shared" si="8"/>
-        <v>66000</v>
-      </c>
-      <c r="I12" s="85"/>
-      <c r="J12" s="140">
+      <c r="G12" s="184">
+        <v>72600.7</v>
+      </c>
+      <c r="H12" s="185">
+        <f t="shared" ref="H11:H17" si="8">G12</f>
+        <v>72600.7</v>
+      </c>
+      <c r="I12" s="83"/>
+      <c r="J12" s="136">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K12" s="86">
+      <c r="K12" s="84">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L12" s="87">
+      <c r="L12" s="85">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M12" s="87">
+        <v>1562.0220000000002</v>
+      </c>
+      <c r="M12" s="85">
         <f t="shared" si="2"/>
-        <v>72600</v>
-      </c>
-      <c r="N12" s="136">
+        <v>86105.199840000001</v>
+      </c>
+      <c r="N12" s="132">
         <f t="shared" si="5"/>
-        <v>72600</v>
-      </c>
-      <c r="O12" s="138" t="str">
+        <v>87667.221839999998</v>
+      </c>
+      <c r="O12" s="134" t="str">
         <f t="shared" si="6"/>
-        <v>$72600,7</v>
-      </c>
-      <c r="P12" s="142" t="str">
+        <v>$87667,7</v>
+      </c>
+      <c r="P12" s="138" t="str">
         <f t="shared" si="7"/>
-        <v>$74778,7</v>
+        <v>$90297,7</v>
       </c>
       <c r="Q12" s="51" t="str">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="72">
+      <c r="B13" s="70">
         <v>23</v>
       </c>
-      <c r="C13" s="72" t="s">
+      <c r="C13" s="70" t="s">
         <v>84</v>
       </c>
-      <c r="D13" s="72" t="s">
+      <c r="D13" s="70" t="s">
         <v>85</v>
       </c>
-      <c r="E13" s="72" t="s">
-        <v>128</v>
-      </c>
-      <c r="F13" s="82">
+      <c r="E13" s="70" t="s">
+        <v>127</v>
+      </c>
+      <c r="F13" s="80">
         <v>6.3</v>
       </c>
-      <c r="G13" s="83">
+      <c r="G13" s="81">
+        <v>138600.23000000001</v>
+      </c>
+      <c r="H13" s="82">
         <v>126000</v>
       </c>
-      <c r="H13" s="84">
-        <f t="shared" si="8"/>
-        <v>126000</v>
-      </c>
-      <c r="I13" s="85"/>
-      <c r="J13" s="140">
+      <c r="I13" s="83"/>
+      <c r="J13" s="136">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K13" s="86">
+        <v>12600.23000000001</v>
+      </c>
+      <c r="K13" s="84">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L13" s="87">
+        <v>630.01150000000052</v>
+      </c>
+      <c r="L13" s="85">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M13" s="87">
+        <v>2982.0419999999999</v>
+      </c>
+      <c r="M13" s="85">
         <f t="shared" si="2"/>
-        <v>138600</v>
-      </c>
-      <c r="N13" s="136">
+        <v>164382.65424</v>
+      </c>
+      <c r="N13" s="132">
         <f t="shared" si="5"/>
-        <v>138600</v>
-      </c>
-      <c r="O13" s="138" t="str">
+        <v>180594.93774000002</v>
+      </c>
+      <c r="O13" s="134" t="str">
         <f t="shared" si="6"/>
-        <v>$138600,23</v>
-      </c>
-      <c r="P13" s="142" t="str">
+        <v>$180595,23</v>
+      </c>
+      <c r="P13" s="138" t="str">
         <f t="shared" si="7"/>
-        <v>$142758,23</v>
+        <v>$186013,23</v>
       </c>
       <c r="Q13" s="51" t="str">
         <f t="shared" si="3"/>
         <v>23</v>
       </c>
       <c r="S13" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="72">
+      <c r="B14" s="70">
         <v>22</v>
       </c>
-      <c r="C14" s="72" t="s">
+      <c r="C14" s="70" t="s">
         <v>86</v>
       </c>
-      <c r="D14" s="72" t="s">
+      <c r="D14" s="70" t="s">
         <v>87</v>
       </c>
-      <c r="E14" s="72" t="s">
-        <v>129</v>
-      </c>
-      <c r="F14" s="82">
+      <c r="E14" s="70" t="s">
+        <v>155</v>
+      </c>
+      <c r="F14" s="80">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G14" s="83">
-        <v>102000</v>
-      </c>
-      <c r="H14" s="84">
-        <f t="shared" si="8"/>
-        <v>102000</v>
-      </c>
-      <c r="I14" s="85"/>
-      <c r="J14" s="140">
+      <c r="G14" s="81">
+        <v>112200.22</v>
+      </c>
+      <c r="H14" s="82">
+        <v>112000</v>
+      </c>
+      <c r="I14" s="83"/>
+      <c r="J14" s="136">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="86">
+        <v>200.22000000000116</v>
+      </c>
+      <c r="K14" s="84">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L14" s="87">
+        <v>10.01100000000006</v>
+      </c>
+      <c r="L14" s="85">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M14" s="87">
+        <v>2414.0339999999997</v>
+      </c>
+      <c r="M14" s="85">
         <f t="shared" si="2"/>
-        <v>112200</v>
-      </c>
-      <c r="N14" s="136">
+        <v>133071.67247999998</v>
+      </c>
+      <c r="N14" s="132">
         <f t="shared" si="5"/>
-        <v>112200</v>
-      </c>
-      <c r="O14" s="138" t="str">
+        <v>135695.93747999999</v>
+      </c>
+      <c r="O14" s="134" t="str">
         <f t="shared" si="6"/>
-        <v>$112200,22</v>
-      </c>
-      <c r="P14" s="142" t="str">
+        <v>$135696,22</v>
+      </c>
+      <c r="P14" s="138" t="str">
         <f t="shared" si="7"/>
-        <v>$115566,22</v>
+        <v>$139767,22</v>
       </c>
       <c r="Q14" s="51" t="str">
         <f>CONCATENATE(B14)</f>
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="72">
+      <c r="B15" s="70">
         <v>21</v>
       </c>
-      <c r="C15" s="72" t="s">
+      <c r="C15" s="70" t="s">
         <v>88</v>
       </c>
-      <c r="D15" s="72" t="s">
+      <c r="D15" s="70" t="s">
         <v>89</v>
       </c>
-      <c r="E15" s="73"/>
-      <c r="F15" s="82">
+      <c r="E15" s="71"/>
+      <c r="F15" s="80">
         <v>8.1999999999999993</v>
       </c>
-      <c r="G15" s="83">
-        <v>164000</v>
-      </c>
-      <c r="H15" s="84">
+      <c r="G15" s="81">
+        <v>180400.21</v>
+      </c>
+      <c r="H15" s="82">
         <f t="shared" si="8"/>
-        <v>164000</v>
-      </c>
-      <c r="I15" s="85"/>
-      <c r="J15" s="140">
+        <v>180400.21</v>
+      </c>
+      <c r="I15" s="83"/>
+      <c r="J15" s="136">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K15" s="86">
+      <c r="K15" s="84">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L15" s="87">
+      <c r="L15" s="85">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M15" s="87">
+        <v>3881.3879999999995</v>
+      </c>
+      <c r="M15" s="85">
         <f t="shared" si="2"/>
-        <v>180399.99999999997</v>
-      </c>
-      <c r="N15" s="136">
+        <v>213958.37535999998</v>
+      </c>
+      <c r="N15" s="132">
         <f t="shared" si="5"/>
-        <v>180399.99999999997</v>
-      </c>
-      <c r="O15" s="138" t="str">
+        <v>217839.76335999998</v>
+      </c>
+      <c r="O15" s="134" t="str">
         <f t="shared" si="6"/>
-        <v>$180400,21</v>
-      </c>
-      <c r="P15" s="142" t="str">
+        <v>$217840,21</v>
+      </c>
+      <c r="P15" s="138" t="str">
         <f t="shared" si="7"/>
-        <v>$185812,21</v>
+        <v>$224375,21</v>
       </c>
       <c r="Q15" s="51" t="str">
         <f t="shared" ref="Q15:Q24" si="9">CONCATENATE(B15)</f>
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="72">
+      <c r="B16" s="70">
         <v>14</v>
       </c>
-      <c r="C16" s="72" t="s">
+      <c r="C16" s="70" t="s">
         <v>90</v>
       </c>
-      <c r="D16" s="72" t="s">
+      <c r="D16" s="70" t="s">
         <v>91</v>
       </c>
-      <c r="E16" s="73"/>
-      <c r="F16" s="82">
+      <c r="E16" s="186" t="s">
+        <v>156</v>
+      </c>
+      <c r="F16" s="80">
         <v>6.1</v>
       </c>
-      <c r="G16" s="83">
-        <v>122000</v>
-      </c>
-      <c r="H16" s="84">
+      <c r="G16" s="81">
+        <v>134200.14000000001</v>
+      </c>
+      <c r="H16" s="82">
         <f t="shared" si="8"/>
-        <v>122000</v>
-      </c>
-      <c r="I16" s="85"/>
-      <c r="J16" s="140">
+        <v>134200.14000000001</v>
+      </c>
+      <c r="I16" s="83"/>
+      <c r="J16" s="136">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K16" s="86">
+      <c r="K16" s="84">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L16" s="87">
+      <c r="L16" s="85">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M16" s="87">
+        <v>2887.3739999999998</v>
+      </c>
+      <c r="M16" s="85">
         <f t="shared" si="2"/>
-        <v>134200</v>
-      </c>
-      <c r="N16" s="136">
+        <v>159164.15727999998</v>
+      </c>
+      <c r="N16" s="132">
         <f t="shared" si="5"/>
-        <v>134200</v>
-      </c>
-      <c r="O16" s="138" t="str">
+        <v>162051.53128</v>
+      </c>
+      <c r="O16" s="134" t="str">
         <f t="shared" si="6"/>
-        <v>$134200,14</v>
-      </c>
-      <c r="P16" s="142" t="str">
+        <v>$162052,14</v>
+      </c>
+      <c r="P16" s="138" t="str">
         <f t="shared" si="7"/>
-        <v>$138226,14</v>
+        <v>$166913,14</v>
       </c>
       <c r="Q16" s="51" t="str">
         <f t="shared" si="9"/>
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="72">
+      <c r="B17" s="70">
         <v>13</v>
       </c>
-      <c r="C17" s="72" t="s">
+      <c r="C17" s="70" t="s">
         <v>92</v>
       </c>
-      <c r="D17" s="72" t="s">
-        <v>121</v>
-      </c>
-      <c r="E17" s="73"/>
-      <c r="F17" s="82">
+      <c r="D17" s="70" t="s">
+        <v>120</v>
+      </c>
+      <c r="E17" s="71"/>
+      <c r="F17" s="80">
         <v>5</v>
       </c>
-      <c r="G17" s="83">
-        <v>100000</v>
-      </c>
-      <c r="H17" s="84">
+      <c r="G17" s="81">
+        <v>110000.13</v>
+      </c>
+      <c r="H17" s="82">
         <f t="shared" si="8"/>
-        <v>100000</v>
-      </c>
-      <c r="I17" s="85"/>
-      <c r="J17" s="140">
+        <v>110000.13</v>
+      </c>
+      <c r="I17" s="83"/>
+      <c r="J17" s="136">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K17" s="86">
+      <c r="K17" s="84">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L17" s="87">
+      <c r="L17" s="85">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M17" s="87">
+        <v>2366.7000000000003</v>
+      </c>
+      <c r="M17" s="85">
         <f t="shared" si="2"/>
-        <v>110000</v>
-      </c>
-      <c r="N17" s="136">
+        <v>130462.424</v>
+      </c>
+      <c r="N17" s="132">
         <f t="shared" si="5"/>
-        <v>110000</v>
-      </c>
-      <c r="O17" s="138" t="str">
+        <v>132829.12400000001</v>
+      </c>
+      <c r="O17" s="134" t="str">
         <f t="shared" si="6"/>
-        <v>$110000,13</v>
-      </c>
-      <c r="P17" s="142" t="str">
+        <v>$132829,13</v>
+      </c>
+      <c r="P17" s="138" t="str">
         <f t="shared" si="7"/>
-        <v>$113300,13</v>
+        <v>$136814,13</v>
       </c>
       <c r="Q17" s="51" t="str">
         <f t="shared" si="9"/>
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="72">
+      <c r="B18" s="70">
         <v>12</v>
       </c>
-      <c r="C18" s="72" t="s">
+      <c r="C18" s="70" t="s">
         <v>93</v>
       </c>
-      <c r="D18" s="72" t="s">
+      <c r="D18" s="70" t="s">
         <v>94</v>
       </c>
-      <c r="E18" s="72" t="s">
-        <v>130</v>
-      </c>
-      <c r="F18" s="82">
+      <c r="E18" s="70" t="s">
+        <v>128</v>
+      </c>
+      <c r="F18" s="80">
         <v>8.1999999999999993</v>
       </c>
-      <c r="G18" s="83">
-        <v>12344183</v>
-      </c>
-      <c r="H18" s="84">
-        <v>164000</v>
-      </c>
-      <c r="I18" s="85"/>
-      <c r="J18" s="140">
+      <c r="G18" s="81">
+        <v>12969592.119999999</v>
+      </c>
+      <c r="H18" s="82">
+        <v>180400</v>
+      </c>
+      <c r="I18" s="83"/>
+      <c r="J18" s="136">
         <f t="shared" si="0"/>
-        <v>12180183</v>
-      </c>
-      <c r="K18" s="86">
+        <v>12789192.119999999</v>
+      </c>
+      <c r="K18" s="84">
         <f t="shared" si="4"/>
-        <v>609009.15</v>
-      </c>
-      <c r="L18" s="87">
+        <v>639459.60600000003</v>
+      </c>
+      <c r="L18" s="85">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M18" s="87">
+        <v>3881.3879999999995</v>
+      </c>
+      <c r="M18" s="85">
         <f t="shared" si="2"/>
-        <v>180399.99999999997</v>
-      </c>
-      <c r="N18" s="136">
+        <v>213958.37535999998</v>
+      </c>
+      <c r="N18" s="132">
         <f t="shared" si="5"/>
-        <v>12969592.15</v>
-      </c>
-      <c r="O18" s="138" t="str">
+        <v>13646491.489360001</v>
+      </c>
+      <c r="O18" s="134" t="str">
         <f t="shared" si="6"/>
-        <v>$12969592,12</v>
-      </c>
-      <c r="P18" s="142" t="str">
+        <v>$13646491,12</v>
+      </c>
+      <c r="P18" s="138" t="str">
         <f t="shared" si="7"/>
-        <v>$13358680,12</v>
+        <v>$14055886,12</v>
       </c>
       <c r="Q18" s="51" t="str">
         <f t="shared" si="9"/>
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="72">
+      <c r="B19" s="70">
         <v>17</v>
       </c>
-      <c r="C19" s="72" t="s">
+      <c r="C19" s="70" t="s">
         <v>95</v>
       </c>
-      <c r="D19" s="72" t="s">
+      <c r="D19" s="70" t="s">
         <v>94</v>
       </c>
-      <c r="E19" s="73"/>
-      <c r="F19" s="82">
+      <c r="E19" s="71"/>
+      <c r="F19" s="80">
         <v>6.1</v>
       </c>
-      <c r="G19" s="83">
-        <v>8363581</v>
-      </c>
-      <c r="H19" s="84"/>
-      <c r="I19" s="85"/>
-      <c r="J19" s="140">
+      <c r="G19" s="81">
+        <v>8915960.1699999999</v>
+      </c>
+      <c r="H19" s="82"/>
+      <c r="I19" s="83"/>
+      <c r="J19" s="136">
         <f t="shared" si="0"/>
-        <v>8363581</v>
-      </c>
-      <c r="K19" s="86">
+        <v>8915960.1699999999</v>
+      </c>
+      <c r="K19" s="84">
         <f t="shared" si="4"/>
-        <v>418179.05000000005</v>
-      </c>
-      <c r="L19" s="87">
+        <v>445798.0085</v>
+      </c>
+      <c r="L19" s="85">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M19" s="87">
+        <v>2887.3739999999998</v>
+      </c>
+      <c r="M19" s="85">
         <f t="shared" si="2"/>
-        <v>134200</v>
-      </c>
-      <c r="N19" s="136">
+        <v>159164.15727999998</v>
+      </c>
+      <c r="N19" s="132">
         <f t="shared" si="5"/>
-        <v>8915960.0500000007</v>
-      </c>
-      <c r="O19" s="138" t="str">
+        <v>9523809.7097800002</v>
+      </c>
+      <c r="O19" s="134" t="str">
         <f t="shared" si="6"/>
-        <v>$8915960,17</v>
-      </c>
-      <c r="P19" s="142" t="str">
+        <v>$9523810,17</v>
+      </c>
+      <c r="P19" s="138" t="str">
         <f t="shared" si="7"/>
-        <v>$9183439,17</v>
+        <v>$9809524,17</v>
       </c>
       <c r="Q19" s="51" t="str">
         <f t="shared" si="9"/>
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="72">
+      <c r="B20" s="70">
         <v>16</v>
       </c>
-      <c r="C20" s="72" t="s">
+      <c r="C20" s="70" t="s">
         <v>96</v>
       </c>
-      <c r="D20" s="72" t="s">
+      <c r="D20" s="70" t="s">
         <v>97</v>
       </c>
-      <c r="E20" s="73" t="s">
-        <v>135</v>
-      </c>
-      <c r="F20" s="82">
+      <c r="E20" s="71" t="s">
+        <v>133</v>
+      </c>
+      <c r="F20" s="80">
         <v>5</v>
       </c>
-      <c r="G20" s="83">
-        <v>100000</v>
-      </c>
-      <c r="H20" s="84">
-        <f>G20</f>
-        <v>100000</v>
-      </c>
-      <c r="I20" s="85"/>
-      <c r="J20" s="140">
+      <c r="G20" s="81">
+        <v>110000.16</v>
+      </c>
+      <c r="H20" s="82">
+        <v>110000</v>
+      </c>
+      <c r="I20" s="83"/>
+      <c r="J20" s="136">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K20" s="86">
+        <v>0.16000000000349246</v>
+      </c>
+      <c r="K20" s="84">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L20" s="87">
+        <v>8.0000000001746226E-3</v>
+      </c>
+      <c r="L20" s="85">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M20" s="87">
+        <v>2366.7000000000003</v>
+      </c>
+      <c r="M20" s="85">
         <f t="shared" si="2"/>
-        <v>110000</v>
-      </c>
-      <c r="N20" s="136">
+        <v>130462.424</v>
+      </c>
+      <c r="N20" s="132">
         <f t="shared" si="5"/>
-        <v>110000</v>
-      </c>
-      <c r="O20" s="138" t="str">
+        <v>132829.29200000002</v>
+      </c>
+      <c r="O20" s="134" t="str">
         <f t="shared" si="6"/>
-        <v>$110000,16</v>
-      </c>
-      <c r="P20" s="142" t="str">
+        <v>$132829,16</v>
+      </c>
+      <c r="P20" s="138" t="str">
         <f t="shared" si="7"/>
-        <v>$113300,16</v>
+        <v>$136814,16</v>
       </c>
       <c r="Q20" s="51" t="str">
         <f t="shared" si="9"/>
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="72">
+      <c r="B21" s="70">
         <v>15</v>
       </c>
-      <c r="C21" s="72" t="s">
+      <c r="C21" s="70" t="s">
         <v>98</v>
       </c>
-      <c r="D21" s="72" t="s">
+      <c r="D21" s="70" t="s">
         <v>99</v>
       </c>
-      <c r="E21" s="72"/>
-      <c r="F21" s="82">
+      <c r="E21" s="70"/>
+      <c r="F21" s="80">
         <v>8.1999999999999993</v>
       </c>
-      <c r="G21" s="83">
-        <v>164000</v>
-      </c>
-      <c r="H21" s="84">
+      <c r="G21" s="81">
+        <v>180400.15</v>
+      </c>
+      <c r="H21" s="82">
         <f>G21</f>
-        <v>164000</v>
-      </c>
-      <c r="I21" s="85"/>
-      <c r="J21" s="140">
+        <v>180400.15</v>
+      </c>
+      <c r="I21" s="83"/>
+      <c r="J21" s="136">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K21" s="86">
+      <c r="K21" s="84">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L21" s="87">
+      <c r="L21" s="85">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M21" s="87">
+        <v>3881.3879999999995</v>
+      </c>
+      <c r="M21" s="85">
         <f t="shared" si="2"/>
-        <v>180399.99999999997</v>
-      </c>
-      <c r="N21" s="136">
+        <v>213958.37535999998</v>
+      </c>
+      <c r="N21" s="132">
         <f t="shared" si="5"/>
-        <v>180399.99999999997</v>
-      </c>
-      <c r="O21" s="138" t="str">
+        <v>217839.76335999998</v>
+      </c>
+      <c r="O21" s="134" t="str">
         <f t="shared" si="6"/>
-        <v>$180400,15</v>
-      </c>
-      <c r="P21" s="142" t="str">
+        <v>$217840,15</v>
+      </c>
+      <c r="P21" s="138" t="str">
         <f t="shared" si="7"/>
-        <v>$185812,15</v>
+        <v>$224375,15</v>
       </c>
       <c r="Q21" s="51" t="str">
         <f t="shared" si="9"/>
@@ -3914,325 +3916,334 @@
       </c>
       <c r="S21" s="50"/>
     </row>
-    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="72">
+      <c r="B22" s="70">
         <v>20</v>
       </c>
-      <c r="C22" s="72" t="s">
+      <c r="C22" s="70" t="s">
         <v>100</v>
       </c>
-      <c r="D22" s="72" t="s">
+      <c r="D22" s="70" t="s">
         <v>101</v>
       </c>
-      <c r="E22" s="73"/>
-      <c r="F22" s="82">
+      <c r="E22" s="71"/>
+      <c r="F22" s="80">
         <v>6.1</v>
       </c>
-      <c r="G22" s="84">
-        <v>122000</v>
-      </c>
-      <c r="H22" s="84">
+      <c r="G22" s="82">
+        <v>134200.20000000001</v>
+      </c>
+      <c r="H22" s="82">
         <f>G22</f>
-        <v>122000</v>
-      </c>
-      <c r="I22" s="85"/>
-      <c r="J22" s="86">
+        <v>134200.20000000001</v>
+      </c>
+      <c r="I22" s="83"/>
+      <c r="J22" s="84">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K22" s="86">
+      <c r="K22" s="84">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L22" s="87">
+      <c r="L22" s="85">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M22" s="87">
+        <v>2887.3739999999998</v>
+      </c>
+      <c r="M22" s="85">
         <f t="shared" si="2"/>
-        <v>134200</v>
-      </c>
-      <c r="N22" s="136">
+        <v>159164.15727999998</v>
+      </c>
+      <c r="N22" s="132">
         <f t="shared" si="5"/>
-        <v>134200</v>
-      </c>
-      <c r="O22" s="138" t="str">
+        <v>162051.53128</v>
+      </c>
+      <c r="O22" s="134" t="str">
         <f t="shared" si="6"/>
-        <v>$134200,20</v>
-      </c>
-      <c r="P22" s="142" t="str">
+        <v>$162052,20</v>
+      </c>
+      <c r="P22" s="138" t="str">
         <f t="shared" si="7"/>
-        <v>$138226,20</v>
+        <v>$166913,20</v>
       </c>
       <c r="Q22" s="51" t="str">
         <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="T22" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="72">
+      <c r="B23" s="70">
         <v>19</v>
       </c>
-      <c r="C23" s="72" t="s">
+      <c r="C23" s="70" t="s">
         <v>102</v>
       </c>
-      <c r="D23" s="72" t="s">
+      <c r="D23" s="70" t="s">
         <v>103</v>
       </c>
-      <c r="E23" s="72"/>
-      <c r="F23" s="82">
+      <c r="E23" s="70"/>
+      <c r="F23" s="80">
         <v>5</v>
       </c>
-      <c r="G23" s="83">
-        <v>100000</v>
-      </c>
-      <c r="H23" s="84">
+      <c r="G23" s="81">
+        <v>110000.19</v>
+      </c>
+      <c r="H23" s="82">
         <f>G23</f>
-        <v>100000</v>
-      </c>
-      <c r="I23" s="85"/>
-      <c r="J23" s="86">
+        <v>110000.19</v>
+      </c>
+      <c r="I23" s="83"/>
+      <c r="J23" s="84">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K23" s="86">
+      <c r="K23" s="84">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L23" s="87">
+      <c r="L23" s="85">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M23" s="87">
+        <v>2366.7000000000003</v>
+      </c>
+      <c r="M23" s="85">
         <f t="shared" si="2"/>
-        <v>110000</v>
-      </c>
-      <c r="N23" s="136">
+        <v>130462.424</v>
+      </c>
+      <c r="N23" s="132">
         <f t="shared" si="5"/>
-        <v>110000</v>
-      </c>
-      <c r="O23" s="138" t="str">
+        <v>132829.12400000001</v>
+      </c>
+      <c r="O23" s="134" t="str">
         <f t="shared" si="6"/>
-        <v>$110000,19</v>
-      </c>
-      <c r="P23" s="142" t="str">
+        <v>$132829,19</v>
+      </c>
+      <c r="P23" s="138" t="str">
         <f t="shared" si="7"/>
-        <v>$113300,19</v>
+        <v>$136814,19</v>
       </c>
       <c r="Q23" s="51" t="str">
         <f t="shared" si="9"/>
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="72">
+      <c r="B24" s="70">
         <v>18</v>
       </c>
-      <c r="C24" s="72" t="s">
+      <c r="C24" s="70" t="s">
         <v>104</v>
       </c>
-      <c r="D24" s="72" t="s">
+      <c r="D24" s="70" t="s">
         <v>105</v>
       </c>
-      <c r="E24" s="73"/>
-      <c r="F24" s="82">
+      <c r="E24" s="71"/>
+      <c r="F24" s="80">
         <v>8.1999999999999993</v>
       </c>
-      <c r="G24" s="83">
-        <v>164000</v>
-      </c>
-      <c r="H24" s="84">
-        <v>168920</v>
-      </c>
-      <c r="I24" s="85"/>
-      <c r="J24" s="86">
+      <c r="G24" s="81">
+        <v>175480.18</v>
+      </c>
+      <c r="H24" s="82">
+        <f>G24</f>
+        <v>175480.18</v>
+      </c>
+      <c r="I24" s="83"/>
+      <c r="J24" s="84">
         <f t="shared" si="0"/>
-        <v>-4920</v>
-      </c>
-      <c r="K24" s="86">
+        <v>0</v>
+      </c>
+      <c r="K24" s="84">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L24" s="87">
+      <c r="L24" s="85">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M24" s="87">
+        <v>3881.3879999999995</v>
+      </c>
+      <c r="M24" s="85">
         <f t="shared" si="2"/>
-        <v>180399.99999999997</v>
-      </c>
-      <c r="N24" s="136">
+        <v>213958.37535999998</v>
+      </c>
+      <c r="N24" s="132">
         <f t="shared" si="5"/>
-        <v>175479.99999999997</v>
-      </c>
-      <c r="O24" s="138" t="str">
+        <v>217839.76335999998</v>
+      </c>
+      <c r="O24" s="134" t="str">
         <f t="shared" si="6"/>
-        <v>$175480,18</v>
-      </c>
-      <c r="P24" s="142" t="str">
+        <v>$217840,18</v>
+      </c>
+      <c r="P24" s="138" t="str">
         <f t="shared" si="7"/>
-        <v>$180744,18</v>
+        <v>$224375,18</v>
       </c>
       <c r="Q24" s="51" t="str">
         <f t="shared" si="9"/>
         <v>18</v>
       </c>
       <c r="T24" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="88"/>
-      <c r="C25" s="89"/>
-      <c r="D25" s="90"/>
-      <c r="E25" s="90"/>
-      <c r="F25" s="91">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="86"/>
+      <c r="C25" s="87"/>
+      <c r="D25" s="88"/>
+      <c r="E25" s="88"/>
+      <c r="F25" s="89">
         <f t="shared" ref="F25:P25" si="10">SUM(F6:F24)</f>
         <v>99.999999999999986</v>
       </c>
       <c r="G25" s="62">
         <f>SUM(G6:G24)</f>
-        <v>22544186</v>
-      </c>
-      <c r="H25" s="70">
+        <v>23902986.899999999</v>
+      </c>
+      <c r="H25" s="68">
         <f t="shared" si="10"/>
-        <v>1874914</v>
+        <v>1915682.4999999998</v>
       </c>
       <c r="I25" s="62">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J25" s="70">
+      <c r="J25" s="68">
         <f t="shared" si="10"/>
-        <v>20669272</v>
-      </c>
-      <c r="K25" s="70">
+        <v>21987304.399999999</v>
+      </c>
+      <c r="K25" s="68">
         <f t="shared" si="10"/>
-        <v>1033709.6000000001</v>
-      </c>
-      <c r="L25" s="70">
+        <v>1099565.19</v>
+      </c>
+      <c r="L25" s="68">
+        <f t="shared" si="10"/>
+        <v>47333.999999999993</v>
+      </c>
+      <c r="M25" s="68">
+        <f t="shared" si="10"/>
+        <v>2609248.4799999995</v>
+      </c>
+      <c r="N25" s="133"/>
+      <c r="O25" s="90">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="M25" s="70">
-        <f t="shared" si="10"/>
-        <v>2200000</v>
-      </c>
-      <c r="N25" s="137"/>
-      <c r="O25" s="92">
+      <c r="P25" s="90">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="P25" s="92">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="59"/>
       <c r="E26" s="59"/>
     </row>
-    <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="1:20" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D28" s="160" t="s">
+    <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:20" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D28" s="154" t="s">
         <v>109</v>
       </c>
-      <c r="E28" s="160"/>
-      <c r="F28" s="160"/>
-      <c r="G28" s="160"/>
-      <c r="H28" s="160"/>
-      <c r="I28" s="160"/>
-      <c r="J28" s="160"/>
-      <c r="K28" s="160"/>
-      <c r="L28" s="160"/>
-      <c r="M28" s="160"/>
-      <c r="N28" s="160"/>
-      <c r="O28" s="160"/>
-    </row>
-    <row r="29" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D29" s="160"/>
-      <c r="E29" s="160"/>
-      <c r="F29" s="160"/>
-      <c r="G29" s="160"/>
-      <c r="H29" s="160"/>
-      <c r="I29" s="160"/>
-      <c r="J29" s="160"/>
-      <c r="K29" s="160"/>
-      <c r="L29" s="160"/>
-      <c r="M29" s="160"/>
-      <c r="N29" s="160"/>
-      <c r="O29" s="160"/>
-    </row>
-    <row r="30" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D30" s="160"/>
-      <c r="E30" s="160"/>
-      <c r="F30" s="160"/>
-      <c r="G30" s="160"/>
-      <c r="H30" s="160"/>
-      <c r="I30" s="160"/>
-      <c r="J30" s="160"/>
-      <c r="K30" s="160"/>
-      <c r="L30" s="160"/>
-      <c r="M30" s="160"/>
-      <c r="N30" s="160"/>
-      <c r="O30" s="160"/>
-    </row>
-    <row r="31" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D31" s="160"/>
-      <c r="E31" s="160"/>
-      <c r="F31" s="160"/>
-      <c r="G31" s="160"/>
-      <c r="H31" s="160"/>
-      <c r="I31" s="160"/>
-      <c r="J31" s="160"/>
-      <c r="K31" s="160"/>
-      <c r="L31" s="160"/>
-      <c r="M31" s="160"/>
-      <c r="N31" s="160"/>
-      <c r="O31" s="160"/>
-    </row>
-    <row r="32" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D32" s="160"/>
-      <c r="E32" s="160"/>
-      <c r="F32" s="160"/>
-      <c r="G32" s="160"/>
-      <c r="H32" s="160"/>
-      <c r="I32" s="160"/>
-      <c r="J32" s="160"/>
-      <c r="K32" s="160"/>
-      <c r="L32" s="160"/>
-      <c r="M32" s="160"/>
-      <c r="N32" s="160"/>
-      <c r="O32" s="160"/>
-    </row>
-    <row r="33" spans="4:15" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D33" s="160"/>
-      <c r="E33" s="160"/>
-      <c r="F33" s="160"/>
-      <c r="G33" s="160"/>
-      <c r="H33" s="160"/>
-      <c r="I33" s="160"/>
-      <c r="J33" s="160"/>
-      <c r="K33" s="160"/>
-      <c r="L33" s="160"/>
-      <c r="M33" s="160"/>
-      <c r="N33" s="160"/>
-      <c r="O33" s="160"/>
+      <c r="E28" s="154"/>
+      <c r="F28" s="154"/>
+      <c r="G28" s="154"/>
+      <c r="H28" s="154"/>
+      <c r="I28" s="154"/>
+      <c r="J28" s="154"/>
+      <c r="K28" s="154"/>
+      <c r="L28" s="154"/>
+      <c r="M28" s="154"/>
+      <c r="N28" s="154"/>
+      <c r="O28" s="154"/>
+    </row>
+    <row r="29" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D29" s="154"/>
+      <c r="E29" s="154"/>
+      <c r="F29" s="154"/>
+      <c r="G29" s="154"/>
+      <c r="H29" s="154"/>
+      <c r="I29" s="154"/>
+      <c r="J29" s="154"/>
+      <c r="K29" s="154"/>
+      <c r="L29" s="154"/>
+      <c r="M29" s="154"/>
+      <c r="N29" s="154"/>
+      <c r="O29" s="154"/>
+    </row>
+    <row r="30" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D30" s="154"/>
+      <c r="E30" s="154"/>
+      <c r="F30" s="154"/>
+      <c r="G30" s="154"/>
+      <c r="H30" s="154"/>
+      <c r="I30" s="154"/>
+      <c r="J30" s="154"/>
+      <c r="K30" s="154"/>
+      <c r="L30" s="154"/>
+      <c r="M30" s="154"/>
+      <c r="N30" s="154"/>
+      <c r="O30" s="154"/>
+    </row>
+    <row r="31" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D31" s="154"/>
+      <c r="E31" s="154"/>
+      <c r="F31" s="154"/>
+      <c r="G31" s="154"/>
+      <c r="H31" s="154"/>
+      <c r="I31" s="154"/>
+      <c r="J31" s="154"/>
+      <c r="K31" s="154"/>
+      <c r="L31" s="154"/>
+      <c r="M31" s="154"/>
+      <c r="N31" s="154"/>
+      <c r="O31" s="154"/>
+    </row>
+    <row r="32" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D32" s="154"/>
+      <c r="E32" s="154"/>
+      <c r="F32" s="154"/>
+      <c r="G32" s="154"/>
+      <c r="H32" s="154"/>
+      <c r="I32" s="154"/>
+      <c r="J32" s="154"/>
+      <c r="K32" s="154"/>
+      <c r="L32" s="154"/>
+      <c r="M32" s="154"/>
+      <c r="N32" s="154"/>
+      <c r="O32" s="154"/>
+    </row>
+    <row r="33" spans="4:15" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D33" s="154"/>
+      <c r="E33" s="154"/>
+      <c r="F33" s="154"/>
+      <c r="G33" s="154"/>
+      <c r="H33" s="154"/>
+      <c r="I33" s="154"/>
+      <c r="J33" s="154"/>
+      <c r="K33" s="154"/>
+      <c r="L33" s="154"/>
+      <c r="M33" s="154"/>
+      <c r="N33" s="154"/>
+      <c r="O33" s="154"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="D28:O33"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
     <mergeCell ref="F1:O1"/>
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="G4:G5"/>
@@ -4244,14 +4255,6 @@
     <mergeCell ref="O3:P3"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="N4:N5"/>
-    <mergeCell ref="D28:O33"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
